--- a/outputs/connact-ai-design-package/connact-ai-feature-roadmap.xlsx
+++ b/outputs/connact-ai-design-package/connact-ai-feature-roadmap.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分期总览" sheetId="1" r:id="R6acfdac15d984933"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能清单" sheetId="2" r:id="R61697a3d0a934759"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI写作流程" sheetId="3" r:id="R211581d251cd42bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接口清单" sheetId="4" r:id="Reedb42e1f54247e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收场景" sheetId="5" r:id="R6f9365536acc46f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分期Prompt" sheetId="6" r:id="Rd53317ac38f64baa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源与说明" sheetId="7" r:id="Rd0cb8aae607d4d00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Overview" sheetId="1" r:id="R67711e996fff4db7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature List" sheetId="2" r:id="R31b3ea6180774f82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Writing Process" sheetId="3" r:id="Rcb24a8cca210435e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API List" sheetId="4" r:id="Ra63401c6cc54413c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acceptance Scenarios" sheetId="5" r:id="R27822523df4c4765"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase Prompts" sheetId="6" r:id="R66ac225c92ef489e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources and Notes" sheetId="7" r:id="Raf3f5b346619457a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -147,7 +147,7 @@
         <x:color rgb="FF21583C"/>
       </x:font>
       <x:fill>
-        <x:patternFill>
+        <x:patternFill patternType="solid">
           <x:bgColor rgb="FFDFF0E5"/>
         </x:patternFill>
       </x:fill>
@@ -157,7 +157,7 @@
         <x:color rgb="FF9B3024"/>
       </x:font>
       <x:fill>
-        <x:patternFill>
+        <x:patternFill patternType="solid">
           <x:bgColor rgb="FFF8E4E1"/>
         </x:patternFill>
       </x:fill>
@@ -170,14 +170,14 @@
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Phases" displayName="Phases" ref="A4:H9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A4:H9"/>
   <x:tableColumns count="8">
-    <x:tableColumn id="1" name="期次"/>
-    <x:tableColumn id="2" name="本期目标"/>
-    <x:tableColumn id="3" name="功能数"/>
-    <x:tableColumn id="4" name="已完成"/>
-    <x:tableColumn id="5" name="完成率"/>
-    <x:tableColumn id="6" name="真实验证数"/>
-    <x:tableColumn id="7" name="入口依赖"/>
-    <x:tableColumn id="8" name="完成边界"/>
+    <x:tableColumn id="1" name="Phase"/>
+    <x:tableColumn id="2" name="Phase Goal"/>
+    <x:tableColumn id="3" name="Features"/>
+    <x:tableColumn id="4" name="Completed"/>
+    <x:tableColumn id="5" name="Completion Rate"/>
+    <x:tableColumn id="6" name="Live Verifications"/>
+    <x:tableColumn id="7" name="Entry Dependency"/>
+    <x:tableColumn id="8" name="Completion Boundary"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -187,17 +187,17 @@
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Features" displayName="Features" ref="A4:L71" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A4:L71"/>
   <x:tableColumns count="12">
-    <x:tableColumn id="1" name="需求ID"/>
-    <x:tableColumn id="2" name="期次"/>
-    <x:tableColumn id="3" name="模块"/>
-    <x:tableColumn id="4" name="功能"/>
-    <x:tableColumn id="5" name="行为与边界"/>
-    <x:tableColumn id="6" name="验收标准"/>
-    <x:tableColumn id="7" name="依赖"/>
-    <x:tableColumn id="8" name="优先级"/>
-    <x:tableColumn id="9" name="实施状态"/>
-    <x:tableColumn id="10" name="验证级别"/>
-    <x:tableColumn id="11" name="验证证据"/>
+    <x:tableColumn id="1" name="Requirement ID"/>
+    <x:tableColumn id="2" name="Phase"/>
+    <x:tableColumn id="3" name="Module"/>
+    <x:tableColumn id="4" name="Feature"/>
+    <x:tableColumn id="5" name="Behavior and Boundaries"/>
+    <x:tableColumn id="6" name="Acceptance Criteria"/>
+    <x:tableColumn id="7" name="Dependencies"/>
+    <x:tableColumn id="8" name="Priority"/>
+    <x:tableColumn id="9" name="Implementation Status"/>
+    <x:tableColumn id="10" name="Verification Level"/>
+    <x:tableColumn id="11" name="Verification Evidence"/>
     <x:tableColumn id="12" name="Prompt"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -208,12 +208,12 @@
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="WritingFlow" displayName="WritingFlow" ref="A4:F16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A4:F16"/>
   <x:tableColumns count="6">
-    <x:tableColumn id="1" name="步骤ID"/>
-    <x:tableColumn id="2" name="交互"/>
-    <x:tableColumn id="3" name="输入"/>
-    <x:tableColumn id="4" name="动作与规则"/>
-    <x:tableColumn id="5" name="输出"/>
-    <x:tableColumn id="6" name="需求ID"/>
+    <x:tableColumn id="1" name="Step ID"/>
+    <x:tableColumn id="2" name="Interaction"/>
+    <x:tableColumn id="3" name="Input"/>
+    <x:tableColumn id="4" name="Actions and Rules"/>
+    <x:tableColumn id="5" name="Output"/>
+    <x:tableColumn id="6" name="Requirement ID"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -223,13 +223,13 @@
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Interfaces" displayName="Interfaces" ref="A4:G19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A4:G19"/>
   <x:tableColumns count="7">
-    <x:tableColumn id="1" name="接口ID"/>
-    <x:tableColumn id="2" name="接口或契约"/>
-    <x:tableColumn id="3" name="期次"/>
-    <x:tableColumn id="4" name="输入"/>
-    <x:tableColumn id="5" name="输出"/>
-    <x:tableColumn id="6" name="关键约束"/>
-    <x:tableColumn id="7" name="需求ID"/>
+    <x:tableColumn id="1" name="API ID"/>
+    <x:tableColumn id="2" name="API or Contract"/>
+    <x:tableColumn id="3" name="Phase"/>
+    <x:tableColumn id="4" name="Input"/>
+    <x:tableColumn id="5" name="Output"/>
+    <x:tableColumn id="6" name="Key Constraints"/>
+    <x:tableColumn id="7" name="Requirement ID"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -239,25 +239,25 @@
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Acceptance" displayName="Acceptance" ref="A4:F26" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A4:F26"/>
   <x:tableColumns count="6">
-    <x:tableColumn id="1" name="测试ID"/>
-    <x:tableColumn id="2" name="期次"/>
-    <x:tableColumn id="3" name="需求ID"/>
-    <x:tableColumn id="4" name="场景"/>
-    <x:tableColumn id="5" name="预期结果"/>
-    <x:tableColumn id="6" name="建议验证证据"/>
+    <x:tableColumn id="1" name="Test ID"/>
+    <x:tableColumn id="2" name="Phase"/>
+    <x:tableColumn id="3" name="Requirement ID"/>
+    <x:tableColumn id="4" name="Scenario"/>
+    <x:tableColumn id="5" name="Expected result"/>
+    <x:tableColumn id="6" name="Recommended Verification Evidence"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Prompts" displayName="Prompts" ref="A4:D42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A4:D42"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Prompts" displayName="Prompts" ref="A4:D50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:D50"/>
   <x:tableColumns count="4">
-    <x:tableColumn id="1" name="期次"/>
-    <x:tableColumn id="2" name="文件"/>
-    <x:tableColumn id="3" name="段落"/>
-    <x:tableColumn id="4" name="Prompt正文"/>
+    <x:tableColumn id="1" name="Phase"/>
+    <x:tableColumn id="2" name="File"/>
+    <x:tableColumn id="3" name="Paragraph"/>
+    <x:tableColumn id="4" name="Prompt Body"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -268,9 +268,9 @@
   <x:autoFilter ref="A4:D15"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="ID"/>
-    <x:tableColumn id="2" name="来源"/>
-    <x:tableColumn id="3" name="地址或位置"/>
-    <x:tableColumn id="4" name="用途"/>
+    <x:tableColumn id="2" name="Source"/>
+    <x:tableColumn id="3" name="Address or Location"/>
+    <x:tableColumn id="4" name="Purpose"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -483,7 +483,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="2" t="str">
-        <x:v>四期开发与 Soon 排期总览</x:v>
+        <x:v>Four-Phase Development and Soon Scheduling Overview</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -495,7 +495,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>范围来自本次确认；功能数量与进度由功能清单计算。无排期承诺，无自动邮件序列。</x:v>
+        <x:v>Scope comes from this confirmation; number of features and progress are calculated from the feature list. No scheduling commitment, no automated email sequence.</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -517,28 +517,28 @@
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="8" t="str">
-        <x:v>期次</x:v>
+        <x:v>Phase</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
-        <x:v>本期目标</x:v>
+        <x:v>Phase Goal</x:v>
       </x:c>
       <x:c r="C4" s="8" t="str">
-        <x:v>功能数</x:v>
+        <x:v>Features</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
-        <x:v>已完成</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E4" s="8" t="str">
-        <x:v>完成率</x:v>
+        <x:v>Completion Rate</x:v>
       </x:c>
       <x:c r="F4" s="8" t="str">
-        <x:v>真实验证数</x:v>
+        <x:v>Live Verifications</x:v>
       </x:c>
       <x:c r="G4" s="8" t="str">
-        <x:v>入口依赖</x:v>
+        <x:v>Entry Dependency</x:v>
       </x:c>
       <x:c r="H4" s="8" t="str">
-        <x:v>完成边界</x:v>
+        <x:v>Completion Boundary</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
@@ -546,14 +546,14 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>简历找人与 AI 写作</x:v>
+        <x:v>Resume search and AI writing</x:v>
       </x:c>
       <x:c r="C5" s="13" t="n">
-        <x:f>COUNTIF('功能清单'!$B$5:$B$71,A5)</x:f>
+        <x:f>COUNTIF('Feature List'!$B$5:$B$71,A5)</x:f>
         <x:v>27</x:v>
       </x:c>
       <x:c r="D5" s="13" t="n">
-        <x:f>COUNTIFS('功能清单'!$B$5:$B$71,A5,'功能清单'!$I$5:$I$71,"已完成")</x:f>
+        <x:f>COUNTIFS('Feature List'!$B$5:$B$71,A5,'Feature List'!$I$5:$I$71,"Completed")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E5" s="15" t="n">
@@ -561,14 +561,14 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="13" t="n">
-        <x:f>COUNTIFS('功能清单'!$B$5:$B$71,A5,'功能清单'!$J$5:$J$71,"真实验证")</x:f>
+        <x:f>COUNTIFS('Feature List'!$B$5:$B$71,A5,'Feature List'!$J$5:$J$71,"Real Verification")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G5" s="5" t="str">
-        <x:v>从空项目开始；外部凭据可缺省并使用显式 Mock</x:v>
+        <x:v>Start from empty project; external credentials can be default and use explicit Mock</x:v>
       </x:c>
       <x:c r="H5" s="5" t="str">
-        <x:v>画像、联系人和草稿持久化；事实有依据；无真实发信</x:v>
+        <x:v>Persona, contact, and draft persistence; facts have basis; no real sending</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="64" customHeight="1">
@@ -576,14 +576,14 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>账户 Gmail 与单封发送</x:v>
+        <x:v>Accounts, Gmail, and Single-Email Sending</x:v>
       </x:c>
       <x:c r="C6" s="14" t="n">
-        <x:f>COUNTIF('功能清单'!$B$5:$B$71,A6)</x:f>
+        <x:f>COUNTIF('Feature List'!$B$5:$B$71,A6)</x:f>
         <x:v>12</x:v>
       </x:c>
       <x:c r="D6" s="14" t="n">
-        <x:f>COUNTIFS('功能清单'!$B$5:$B$71,A6,'功能清单'!$I$5:$I$71,"已完成")</x:f>
+        <x:f>COUNTIFS('Feature List'!$B$5:$B$71,A6,'Feature List'!$I$5:$I$71,"Completed")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E6" s="16" t="n">
@@ -591,14 +591,14 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="14" t="n">
-        <x:f>COUNTIFS('功能清单'!$B$5:$B$71,A6,'功能清单'!$J$5:$J$71,"真实验证")</x:f>
+        <x:f>COUNTIFS('Feature List'!$B$5:$B$71,A6,'Feature List'!$J$5:$J$71,"Real Verification")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G6" s="9" t="str">
-        <x:v>P1 草稿和工作区边界稳定</x:v>
+        <x:v>P1 draft and workspace boundaries stable</x:v>
       </x:c>
       <x:c r="H6" s="9" t="str">
-        <x:v>两用户隔离；指定邮箱真实发信或如实标未验证；幂等/unknown 处理</x:v>
+        <x:v>Two-user isolation; specified email real sending or truthfully mark unverified; idempotent/unknown handling</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="64" customHeight="1">
@@ -606,14 +606,14 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>收件箱与手动跟进</x:v>
+        <x:v>Inbox and manual follow-up</x:v>
       </x:c>
       <x:c r="C7" s="13" t="n">
-        <x:f>COUNTIF('功能清单'!$B$5:$B$71,A7)</x:f>
+        <x:f>COUNTIF('Feature List'!$B$5:$B$71,A7)</x:f>
         <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="13" t="n">
-        <x:f>COUNTIFS('功能清单'!$B$5:$B$71,A7,'功能清单'!$I$5:$I$71,"已完成")</x:f>
+        <x:f>COUNTIFS('Feature List'!$B$5:$B$71,A7,'Feature List'!$I$5:$I$71,"Completed")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E7" s="15" t="n">
@@ -621,14 +621,14 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F7" s="13" t="n">
-        <x:f>COUNTIFS('功能清单'!$B$5:$B$71,A7,'功能清单'!$J$5:$J$71,"真实验证")</x:f>
+        <x:f>COUNTIFS('Feature List'!$B$5:$B$71,A7,'Feature List'!$J$5:$J$71,"Real Verification")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G7" s="5" t="str">
-        <x:v>P2 授权与发送稳定</x:v>
+        <x:v>P2 Authorization and sending stability</x:v>
       </x:c>
       <x:c r="H7" s="5" t="str">
-        <x:v>真实回复同步；到期只提醒；新回复暂停既有排期</x:v>
+        <x:v>Real reply synchronization; expiration only reminder; new replies pause existing schedule</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="64" customHeight="1">
@@ -636,14 +636,14 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>批量活动模板与统计</x:v>
+        <x:v>Campaign Templates and Analytics</x:v>
       </x:c>
       <x:c r="C8" s="14" t="n">
-        <x:f>COUNTIF('功能清单'!$B$5:$B$71,A8)</x:f>
+        <x:f>COUNTIF('Feature List'!$B$5:$B$71,A8)</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="D8" s="14" t="n">
-        <x:f>COUNTIFS('功能清单'!$B$5:$B$71,A8,'功能清单'!$I$5:$I$71,"已完成")</x:f>
+        <x:f>COUNTIFS('Feature List'!$B$5:$B$71,A8,'Feature List'!$I$5:$I$71,"Completed")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E8" s="16" t="n">
@@ -651,14 +651,14 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F8" s="14" t="n">
-        <x:f>COUNTIFS('功能清单'!$B$5:$B$71,A8,'功能清单'!$J$5:$J$71,"真实验证")</x:f>
+        <x:f>COUNTIFS('Feature List'!$B$5:$B$71,A8,'Feature List'!$J$5:$J$71,"Real Verification")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G8" s="9" t="str">
-        <x:v>P3 同步与回复保护稳定</x:v>
+        <x:v>P3 Synchronization and Reply Protection Stable</x:v>
       </x:c>
       <x:c r="H8" s="9" t="str">
-        <x:v>逐人发送、取消生效、统计口径可核对；Academic 仅契约</x:v>
+        <x:v>Per-recipient sending, effective cancellation, and verifiable metric definitions; Academic remains contract-only</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="64" customHeight="1">
@@ -666,14 +666,14 @@
         <x:v>Soon</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>管理员后端</x:v>
+        <x:v>Administrator Backend</x:v>
       </x:c>
       <x:c r="C9" s="13" t="n">
-        <x:f>COUNTIF('功能清单'!$B$5:$B$71,A9)</x:f>
+        <x:f>COUNTIF('Feature List'!$B$5:$B$71,A9)</x:f>
         <x:v>9</x:v>
       </x:c>
       <x:c r="D9" s="13" t="n">
-        <x:f>COUNTIFS('功能清单'!$B$5:$B$71,A9,'功能清单'!$I$5:$I$71,"已完成")</x:f>
+        <x:f>COUNTIFS('Feature List'!$B$5:$B$71,A9,'Feature List'!$I$5:$I$71,"Completed")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="E9" s="15" t="n">
@@ -681,19 +681,19 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F9" s="13" t="n">
-        <x:f>COUNTIFS('功能清单'!$B$5:$B$71,A9,'功能清单'!$J$5:$J$71,"真实验证")</x:f>
+        <x:f>COUNTIFS('Feature List'!$B$5:$B$71,A9,'Feature List'!$J$5:$J$71,"Real Verification")</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="G9" s="5" t="str">
-        <x:v>账户、平台角色及对应业务模块</x:v>
+        <x:v>Accounts, platform roles, and corresponding business modules</x:v>
       </x:c>
       <x:c r="H9" s="5" t="str">
-        <x:v>仅规划占位；具体期次和日期待定</x:v>
+        <x:v>Planning placeholder only; the phase and date are not scheduled</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="17" t="str">
-        <x:v>使用顺序</x:v>
+        <x:v>Usage Order</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="28" customHeight="1">
@@ -701,10 +701,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>先看 HTML</x:v>
+        <x:v>First Look at HTML</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>流程与架构为离线演示；所有数据虚构。</x:v>
+        <x:v>Process and Architecture are for offline demo; all data is fictional.</x:v>
       </x:c>
       <x:c r="D12"/>
       <x:c r="E12"/>
@@ -717,10 +717,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>再看 Word</x:v>
+        <x:v>Then Look at Word</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>AI写作交互、状态、数据与错误契约。</x:v>
+        <x:v>AI Writing Interaction, Status, Data, and Error Contracts</x:v>
       </x:c>
       <x:c r="D13"/>
       <x:c r="E13"/>
@@ -733,10 +733,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>筛选功能清单</x:v>
+        <x:v>Filter Feature List</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>按期次筛选，更新实施状态与验证证据。</x:v>
+        <x:v>Filter by Phase, Update Implementation Status and Verification Evidence</x:v>
       </x:c>
       <x:c r="D14"/>
       <x:c r="E14"/>
@@ -749,10 +749,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>使用分期 Prompt</x:v>
+        <x:v>Use Phase Prompts</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>每期内容在分期Prompt页；也提供4个独立MD文件。</x:v>
+        <x:v>Each phase's content is on the Phase Prompts sheet and in a separate Markdown file.</x:v>
       </x:c>
       <x:c r="D15"/>
       <x:c r="E15"/>
@@ -762,13 +762,13 @@
     </x:row>
     <x:row r="16" ht="28" customHeight="1">
       <x:c r="A16" t="str">
-        <x:v>范围</x:v>
+        <x:v>Scope</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>Academic仅预留</x:v>
+        <x:v>Academic is Reserved Only</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>登录移至P2；不做自动序列、团队协作、计费或Outlook。</x:v>
+        <x:v>Login is moved to P2; no automated sequence, team collaboration, billing, or Outlook</x:v>
       </x:c>
       <x:c r="D16"/>
       <x:c r="E16"/>
@@ -779,7 +779,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R754fec25b0f4479d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2663030ee4b4ebf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -804,7 +804,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="2" t="str">
-        <x:v>Connact.ai 分期功能清单</x:v>
+        <x:v>Connact.ai Phase Feature List</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -820,7 +820,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>状态为产品实施状态；当前均未开发。淡黄色列供后续更新，验证需填实际证据。</x:v>
+        <x:v>Status represents product implementation status; all are currently undeveloped. Light yellow column is for future updates, verification requires actual evidence.</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -850,37 +850,37 @@
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="8" t="str">
-        <x:v>需求ID</x:v>
+        <x:v>Requirement ID</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
-        <x:v>期次</x:v>
+        <x:v>Phase</x:v>
       </x:c>
       <x:c r="C4" s="8" t="str">
-        <x:v>模块</x:v>
+        <x:v>Module</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
-        <x:v>功能</x:v>
+        <x:v>Feature</x:v>
       </x:c>
       <x:c r="E4" s="8" t="str">
-        <x:v>行为与边界</x:v>
+        <x:v>Behavior and Boundaries</x:v>
       </x:c>
       <x:c r="F4" s="8" t="str">
-        <x:v>验收标准</x:v>
+        <x:v>Acceptance Criteria</x:v>
       </x:c>
       <x:c r="G4" s="8" t="str">
-        <x:v>依赖</x:v>
+        <x:v>Dependencies</x:v>
       </x:c>
       <x:c r="H4" s="8" t="str">
-        <x:v>优先级</x:v>
+        <x:v>Priority</x:v>
       </x:c>
       <x:c r="I4" s="8" t="str">
-        <x:v>实施状态</x:v>
+        <x:v>Implementation Status</x:v>
       </x:c>
       <x:c r="J4" s="8" t="str">
-        <x:v>验证级别</x:v>
+        <x:v>Verification Level</x:v>
       </x:c>
       <x:c r="K4" s="8" t="str">
-        <x:v>验证证据</x:v>
+        <x:v>Verification Evidence</x:v>
       </x:c>
       <x:c r="L4" s="8" t="str">
         <x:v>Prompt</x:v>
@@ -894,28 +894,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>工作台</x:v>
+        <x:v>Workspace</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>全局布局与入口</x:v>
+        <x:v>Global layout and entry point</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>左导航、顶部、主区及联系人抽屉；未来页面占位</x:v>
+        <x:v>Left navigation, top, main area, and contact drawer; future page placeholders</x:v>
       </x:c>
       <x:c r="F5" s="5" t="str">
-        <x:v>可独立进入画像、搜索、联系人、编辑器；占位无假操作</x:v>
+        <x:v>Can be independently accessed to persona, search, contacts, and editor; placeholders have no fake operations</x:v>
       </x:c>
       <x:c r="G5" s="5" t="str">
-        <x:v>无</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="H5" s="5" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I5" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J5" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K5" s="12" t="str"/>
       <x:c r="L5" s="5" t="str">
@@ -930,16 +930,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>工作台</x:v>
+        <x:v>Workspace</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>中英文界面</x:v>
+        <x:v>Chinese and English interface</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
-        <x:v>英文默认，核心文案及错误支持中文；邮件语言独立</x:v>
+        <x:v>English is default, core text and error messages support Chinese; email language is independent</x:v>
       </x:c>
       <x:c r="F6" s="9" t="str">
-        <x:v>切换界面不改变用户正文；设置刷新后保留</x:v>
+        <x:v>Switching interface does not change user body text; settings are retained after refresh</x:v>
       </x:c>
       <x:c r="G6" s="9" t="str">
         <x:v>P1-01</x:v>
@@ -948,10 +948,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I6" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J6" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K6" s="12" t="str"/>
       <x:c r="L6" s="9" t="str">
@@ -966,28 +966,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>工作台</x:v>
+        <x:v>Workspace</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>工作区与持久化</x:v>
+        <x:v>Workspace and persistence</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>本地固定 workspace；后端查询始终限定归属</x:v>
+        <x:v>Local fixed workspace; backend queries are always limited to ownership</x:v>
       </x:c>
       <x:c r="F7" s="5" t="str">
-        <x:v>跨工作区测试无法读取另一工作区数据；开发登录仅本地启用</x:v>
+        <x:v>Cross-workspace testing cannot read data from another workspace; development login is only enabled locally</x:v>
       </x:c>
       <x:c r="G7" s="5" t="str">
-        <x:v>无</x:v>
+        <x:v>None</x:v>
       </x:c>
       <x:c r="H7" s="5" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I7" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J7" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K7" s="12" t="str"/>
       <x:c r="L7" s="5" t="str">
@@ -1002,16 +1002,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>工作台</x:v>
+        <x:v>Workspace</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>Dashboard 与 Finance</x:v>
+        <x:v>Dashboard and Finance</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>使用真实本地数量、最近联系人和草稿</x:v>
+        <x:v>Use real local quantity, recent contacts, and drafts</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
-        <x:v>与数据库一致；无数据时显示空状态</x:v>
+        <x:v>Consistent with the database; display empty state when no data</x:v>
       </x:c>
       <x:c r="G8" s="9" t="str">
         <x:v>P1-03</x:v>
@@ -1020,10 +1020,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I8" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J8" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K8" s="12" t="str"/>
       <x:c r="L8" s="9" t="str">
@@ -1038,16 +1038,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>工作台</x:v>
+        <x:v>Workspace</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>Academic 占位</x:v>
+        <x:v>Academic placeholder</x:v>
       </x:c>
       <x:c r="E9" s="5" t="str">
-        <x:v>入口、未来流程及领域扩展位置</x:v>
+        <x:v>Entry point, future process, and domain extension location</x:v>
       </x:c>
       <x:c r="F9" s="5" t="str">
-        <x:v>没有伪造导师或可点击的假搜索</x:v>
+        <x:v>No fake mentors or clickable fake search</x:v>
       </x:c>
       <x:c r="G9" s="5" t="str">
         <x:v>P1-01</x:v>
@@ -1056,10 +1056,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I9" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J9" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K9" s="12" t="str"/>
       <x:c r="L9" s="5" t="str">
@@ -1074,16 +1074,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>画像</x:v>
+        <x:v>Persona</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>简历上传</x:v>
+        <x:v>Resume upload</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>文本 PDF/DOCX，10 MB 上限，私有文件</x:v>
+        <x:v>Text PDF/DOCX, 10 MB limit, private file</x:v>
       </x:c>
       <x:c r="F10" s="9" t="str">
-        <x:v>超限/不支持类型被拒；未实现 OCR 时明确提示</x:v>
+        <x:v>Exceeding limit or unsupported types are rejected; clearly prompt when OCR is not implemented</x:v>
       </x:c>
       <x:c r="G10" s="9" t="str">
         <x:v>P1-03</x:v>
@@ -1092,10 +1092,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I10" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J10" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K10" s="12" t="str"/>
       <x:c r="L10" s="9" t="str">
@@ -1110,16 +1110,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
-        <x:v>画像</x:v>
+        <x:v>Persona</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
-        <x:v>解析与人工确认</x:v>
+        <x:v>Parsing and manual confirmation</x:v>
       </x:c>
       <x:c r="E11" s="5" t="str">
-        <x:v>字段提取、来源片段、编辑后创建画像版本</x:v>
+        <x:v>Field extraction, source snippets, and create persona version after editing</x:v>
       </x:c>
       <x:c r="F11" s="5" t="str">
-        <x:v>修改学校/经历后生成新版本；未确认不作为已确认事实</x:v>
+        <x:v>Generate new version after modifying school/experience; unconfirmed does not count as confirmed fact</x:v>
       </x:c>
       <x:c r="G11" s="5" t="str">
         <x:v>P1-06</x:v>
@@ -1128,10 +1128,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I11" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J11" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K11" s="12" t="str"/>
       <x:c r="L11" s="5" t="str">
@@ -1146,16 +1146,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>画像</x:v>
+        <x:v>Persona</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>手动及多画像</x:v>
+        <x:v>Manual and multiple personas</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>职业目的、金融领域、地区、教育/工作经历</x:v>
+        <x:v>Career purpose, financial domain, region, education/work experience</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
-        <x:v>不上传也可保存；可切换多个画像</x:v>
+        <x:v>Can be saved without upload; can switch multiple personas</x:v>
       </x:c>
       <x:c r="G12" s="9" t="str">
         <x:v>P1-03</x:v>
@@ -1164,10 +1164,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I12" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J12" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K12" s="12" t="str"/>
       <x:c r="L12" s="9" t="str">
@@ -1182,16 +1182,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C13" s="5" t="str">
-        <x:v>搜索</x:v>
+        <x:v>Search</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
-        <x:v>基础人员搜索</x:v>
+        <x:v>Basic people search</x:v>
       </x:c>
       <x:c r="E13" s="5" t="str">
-        <x:v>Apollo 结构化人员查询；结果辅助定位 LinkedIn 公开档案</x:v>
+        <x:v>Apollo structured people query; results assist in locating LinkedIn public profile</x:v>
       </x:c>
       <x:c r="F13" s="5" t="str">
-        <x:v>条件真实传递；错误、空结果和分页分别展示</x:v>
+        <x:v>Conditions are truthfully passed; errors, empty results, and pagination are separately displayed</x:v>
       </x:c>
       <x:c r="G13" s="5" t="str">
         <x:v>P1-03</x:v>
@@ -1200,10 +1200,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I13" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J13" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K13" s="12" t="str"/>
       <x:c r="L13" s="5" t="str">
@@ -1218,16 +1218,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>搜索</x:v>
+        <x:v>Search</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>按需信息补充</x:v>
+        <x:v>On-demand information enrichment</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
-        <x:v>Apollo 按需补充邮箱及详情；核对后的 LinkedIn 档案辅助匹配</x:v>
+        <x:v>Apollo on-demand enrichment of email and details; verified LinkedIn profile assists in matching</x:v>
       </x:c>
       <x:c r="F14" s="9" t="str">
-        <x:v>搜索无邮箱不报成功补充；无结果保留 unknown</x:v>
+        <x:v>Search without email does not report successful enrichment; no results retain unknown</x:v>
       </x:c>
       <x:c r="G14" s="9" t="str">
         <x:v>P1-09</x:v>
@@ -1236,10 +1236,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I14" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J14" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K14" s="12" t="str"/>
       <x:c r="L14" s="9" t="str">
@@ -1254,16 +1254,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C15" s="5" t="str">
-        <x:v>搜索</x:v>
+        <x:v>Search</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
-        <x:v>LinkedIn 资料与双源证据</x:v>
+        <x:v>LinkedIn profile and dual-source evidence</x:v>
       </x:c>
       <x:c r="E15" s="5" t="str">
-        <x:v>SerpAPI 检索 LinkedIn 公开档案；与 Apollo 关联互补，保留来源、时间与冲突</x:v>
+        <x:v>SerpAPI retrieves LinkedIn public profile; associated with Apollo for complement, retain source, time, and conflicts</x:v>
       </x:c>
       <x:c r="F15" s="5" t="str">
-        <x:v>摘要标待核实；同名不自动合并，冲突不覆盖；定向检索与反向匹配须真实验证</x:v>
+        <x:v>Summary marked as pending verification; same name does not auto-merge, conflicts do not override; directed search and reverse matching require real verification</x:v>
       </x:c>
       <x:c r="G15" s="5" t="str">
         <x:v>P1-09</x:v>
@@ -1272,10 +1272,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I15" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J15" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K15" s="12" t="str"/>
       <x:c r="L15" s="5" t="str">
@@ -1290,28 +1290,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>搜索</x:v>
+        <x:v>Search</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>AI 推荐理由</x:v>
+        <x:v>AI recommendation rationale</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
-        <x:v>选定画像与双源已核实事实比较；记录画像版本，待核实摘要不作为写信事实</x:v>
+        <x:v>Selected persona and dual-source verified facts compared; record persona version, pending verification summary does not count as writing fact</x:v>
       </x:c>
       <x:c r="F16" s="9" t="str">
-        <x:v>无证据不编造校友；不同画像推荐不混用</x:v>
+        <x:v>No evidence, no fabrication of alumni; different persona recommendations are not mixed</x:v>
       </x:c>
       <x:c r="G16" s="9" t="str">
-        <x:v>P1-07、P1-11</x:v>
+        <x:v>P1-07, P1-11</x:v>
       </x:c>
       <x:c r="H16" s="9" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I16" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J16" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K16" s="12" t="str"/>
       <x:c r="L16" s="9" t="str">
@@ -1326,16 +1326,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C17" s="5" t="str">
-        <x:v>搜索</x:v>
+        <x:v>Search</x:v>
       </x:c>
       <x:c r="D17" s="5" t="str">
-        <x:v>保存与去重</x:v>
+        <x:v>Save and deduplication</x:v>
       </x:c>
       <x:c r="E17" s="5" t="str">
-        <x:v>单人/批量保存；提供商 ID 优先</x:v>
+        <x:v>Single person/batch save; provider ID priority</x:v>
       </x:c>
       <x:c r="F17" s="5" t="str">
-        <x:v>相同来源记录二次保存不重复；同名不自动合并</x:v>
+        <x:v>Same source records not duplicated on secondary save; same name does not auto-merge</x:v>
       </x:c>
       <x:c r="G17" s="5" t="str">
         <x:v>P1-09</x:v>
@@ -1344,10 +1344,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I17" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J17" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K17" s="12" t="str"/>
       <x:c r="L17" s="5" t="str">
@@ -1362,16 +1362,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>联系人</x:v>
+        <x:v>Contact</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>联系人基础管理</x:v>
+        <x:v>Contact basic management</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
-        <x:v>手动新增、详情、标签/简单列表、备注</x:v>
+        <x:v>Manual add, details, tags/simple list, notes</x:v>
       </x:c>
       <x:c r="F18" s="9" t="str">
-        <x:v>刷新后保存；能从详情进入写信</x:v>
+        <x:v>Saved after refresh; can enter writing from details</x:v>
       </x:c>
       <x:c r="G18" s="9" t="str">
         <x:v>P1-03</x:v>
@@ -1380,10 +1380,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I18" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J18" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K18" s="12" t="str"/>
       <x:c r="L18" s="9" t="str">
@@ -1398,16 +1398,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C19" s="5" t="str">
-        <x:v>联系人</x:v>
+        <x:v>Contact</x:v>
       </x:c>
       <x:c r="D19" s="5" t="str">
-        <x:v>领域资料和邮箱状态</x:v>
+        <x:v>Domain data and email status</x:v>
       </x:c>
       <x:c r="E19" s="5" t="str">
-        <x:v>共享 Contact + 领域扩展；邮箱状态独立</x:v>
+        <x:v>Shared Contact + domain extension; email status is independent</x:v>
       </x:c>
       <x:c r="F19" s="5" t="str">
-        <x:v>同人可关联多个领域；verified 不显示为保证送达</x:v>
+        <x:v>Same person can associate multiple domains; verified does not display as guaranteed delivery</x:v>
       </x:c>
       <x:c r="G19" s="5" t="str">
         <x:v>P1-14</x:v>
@@ -1416,10 +1416,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I19" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J19" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K19" s="12" t="str"/>
       <x:c r="L19" s="5" t="str">
@@ -1434,28 +1434,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C20" s="9" t="str">
-        <x:v>AI 写作</x:v>
+        <x:v>AI writing</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>写作 Brief</x:v>
+        <x:v>Writing Brief</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>联系人、画像、目的、CTA、语言、语气、长度</x:v>
+        <x:v>Contact, persona, purpose, CTA, language, tone, length</x:v>
       </x:c>
       <x:c r="F20" s="9" t="str">
-        <x:v>没有画像可手写；生成缺少必要背景时定位缺失项</x:v>
+        <x:v>No persona can be handwritten; generate missing necessary background and locate missing items</x:v>
       </x:c>
       <x:c r="G20" s="9" t="str">
-        <x:v>P1-08、P1-14</x:v>
+        <x:v>P1-08, P1-14</x:v>
       </x:c>
       <x:c r="H20" s="9" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I20" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J20" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K20" s="12" t="str"/>
       <x:c r="L20" s="9" t="str">
@@ -1470,28 +1470,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C21" s="5" t="str">
-        <x:v>AI 写作</x:v>
+        <x:v>AI writing</x:v>
       </x:c>
       <x:c r="D21" s="5" t="str">
-        <x:v>证据选择</x:v>
+        <x:v>Evidence selection</x:v>
       </x:c>
       <x:c r="E21" s="5" t="str">
-        <x:v>可选事实、来源、未知项；选择允许用于邮件的事实</x:v>
+        <x:v>Optional facts, sources, unknown items; select facts for use in email</x:v>
       </x:c>
       <x:c r="F21" s="5" t="str">
-        <x:v>未选择或未知事实不能被自动编成肯定句</x:v>
+        <x:v>Unselected or unknown facts cannot be automatically compiled into affirmative statements</x:v>
       </x:c>
       <x:c r="G21" s="5" t="str">
-        <x:v>P1-11、P1-16</x:v>
+        <x:v>P1-11, P1-16</x:v>
       </x:c>
       <x:c r="H21" s="5" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I21" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J21" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K21" s="12" t="str"/>
       <x:c r="L21" s="5" t="str">
@@ -1506,16 +1506,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C22" s="9" t="str">
-        <x:v>AI 写作</x:v>
+        <x:v>AI writing</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>生成建议</x:v>
+        <x:v>Generation suggestions</x:v>
       </x:c>
       <x:c r="E22" s="9" t="str">
-        <x:v>结构化 subject/body/claims/warnings；建议区展示</x:v>
+        <x:v>Structured subject/body/claims/warnings; suggestions area display</x:v>
       </x:c>
       <x:c r="F22" s="9" t="str">
-        <x:v>生成不覆盖已编辑正文；失败保留当前稿</x:v>
+        <x:v>Generation does not overwrite edited body; failed saves retain current draft</x:v>
       </x:c>
       <x:c r="G22" s="9" t="str">
         <x:v>P1-17</x:v>
@@ -1524,10 +1524,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I22" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J22" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K22" s="12" t="str"/>
       <x:c r="L22" s="9" t="str">
@@ -1542,16 +1542,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
-        <x:v>AI 写作</x:v>
+        <x:v>AI writing</x:v>
       </x:c>
       <x:c r="D23" s="5" t="str">
-        <x:v>用户采纳</x:v>
+        <x:v>User adoption</x:v>
       </x:c>
       <x:c r="E23" s="5" t="str">
-        <x:v>显示当前稿与建议稿；采纳/丢弃/撤销</x:v>
+        <x:v>Display current draft and suggestion draft; adopt/discard/revert</x:v>
       </x:c>
       <x:c r="F23" s="5" t="str">
-        <x:v>采纳生成新版本；可恢复上一稿</x:v>
+        <x:v>Adopt generates new version; can revert to previous draft</x:v>
       </x:c>
       <x:c r="G23" s="5" t="str">
         <x:v>P1-18</x:v>
@@ -1560,10 +1560,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I23" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J23" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K23" s="12" t="str"/>
       <x:c r="L23" s="5" t="str">
@@ -1578,16 +1578,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C24" s="9" t="str">
-        <x:v>AI 写作</x:v>
+        <x:v>AI writing</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>局部改写</x:v>
+        <x:v>Partial rewriting</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
-        <x:v>选中文本后缩短、语气改写；版本校验</x:v>
+        <x:v>Select text to shorten, tone rewrite; version validation</x:v>
       </x:c>
       <x:c r="F24" s="9" t="str">
-        <x:v>编辑期间返回旧结果不会覆盖新稿；只替换选区</x:v>
+        <x:v>Editing returns old results without overwriting new draft; only replace selected area</x:v>
       </x:c>
       <x:c r="G24" s="9" t="str">
         <x:v>P1-19</x:v>
@@ -1596,10 +1596,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I24" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J24" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K24" s="12" t="str"/>
       <x:c r="L24" s="9" t="str">
@@ -1614,16 +1614,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C25" s="5" t="str">
-        <x:v>AI 写作</x:v>
+        <x:v>AI writing</x:v>
       </x:c>
       <x:c r="D25" s="5" t="str">
-        <x:v>富文本与变量</x:v>
+        <x:v>Rich text and variables</x:v>
       </x:c>
       <x:c r="E25" s="5" t="str">
-        <x:v>Tiptap 基础格式、变量节点及来源映射</x:v>
+        <x:v>Tiptap basic formatting, variable nodes, and source mapping</x:v>
       </x:c>
       <x:c r="F25" s="5" t="str">
-        <x:v>链接和列表可用；原始文档结构可持久化</x:v>
+        <x:v>Links and lists are available; original document structure can be persisted</x:v>
       </x:c>
       <x:c r="G25" s="5" t="str">
         <x:v>P1-16</x:v>
@@ -1632,10 +1632,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I25" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J25" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K25" s="12" t="str"/>
       <x:c r="L25" s="5" t="str">
@@ -1650,16 +1650,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C26" s="9" t="str">
-        <x:v>AI 写作</x:v>
+        <x:v>AI writing</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>联系人效果预览</x:v>
+        <x:v>Contact effect preview</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
-        <x:v>正文及主题渲染变量；显示 missing 列表</x:v>
+        <x:v>Body and subject rendering variables; display missing list</x:v>
       </x:c>
       <x:c r="F26" s="9" t="str">
-        <x:v>未知变量阻止标为 Ready；不同联系人预览正确</x:v>
+        <x:v>Unknown variables prevent marking as Ready; correct preview for different contacts</x:v>
       </x:c>
       <x:c r="G26" s="9" t="str">
         <x:v>P1-21</x:v>
@@ -1668,10 +1668,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I26" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J26" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K26" s="12" t="str"/>
       <x:c r="L26" s="9" t="str">
@@ -1686,16 +1686,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C27" s="5" t="str">
-        <x:v>AI 写作</x:v>
+        <x:v>AI writing</x:v>
       </x:c>
       <x:c r="D27" s="5" t="str">
-        <x:v>自动保存与冲突</x:v>
+        <x:v>Auto-save and conflict</x:v>
       </x:c>
       <x:c r="E27" s="5" t="str">
-        <x:v>防抖保存、revision、409 冲突和错误状态</x:v>
+        <x:v>Debounce save, revision, 409 conflict, and error status</x:v>
       </x:c>
       <x:c r="F27" s="5" t="str">
-        <x:v>刷新可恢复；保存失败不显示 Saved；冲突保留两份</x:v>
+        <x:v>Refresh can recover; save failure does not display Saved; conflict retains both versions</x:v>
       </x:c>
       <x:c r="G27" s="5" t="str">
         <x:v>P1-19</x:v>
@@ -1704,10 +1704,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I27" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J27" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K27" s="12" t="str"/>
       <x:c r="L27" s="5" t="str">
@@ -1722,28 +1722,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C28" s="9" t="str">
-        <x:v>AI 写作</x:v>
+        <x:v>AI writing</x:v>
       </x:c>
       <x:c r="D28" s="9" t="str">
-        <x:v>草稿库和复制</x:v>
+        <x:v>Draft library and copy</x:v>
       </x:c>
       <x:c r="E28" s="9" t="str">
-        <x:v>按联系人查草稿；复制主题/纯文本；Finance 起点</x:v>
+        <x:v>Search drafts by contact; copy subject/pure text; Finance starting point</x:v>
       </x:c>
       <x:c r="F28" s="9" t="str">
-        <x:v>复制结果与最终预览一致；不出现发送成功</x:v>
+        <x:v>Copy result matches final preview; no send success appears</x:v>
       </x:c>
       <x:c r="G28" s="9" t="str">
-        <x:v>P1-22、P1-23</x:v>
+        <x:v>P1-22, P1-23</x:v>
       </x:c>
       <x:c r="H28" s="9" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I28" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J28" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K28" s="12" t="str"/>
       <x:c r="L28" s="9" t="str">
@@ -1758,16 +1758,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C29" s="5" t="str">
-        <x:v>AI 写作</x:v>
+        <x:v>AI writing</x:v>
       </x:c>
       <x:c r="D29" s="5" t="str">
-        <x:v>AI 运行记录</x:v>
+        <x:v>AI operation record</x:v>
       </x:c>
       <x:c r="E29" s="5" t="str">
-        <x:v>模型、提示词版本、事实 ID、输入版本、耗时与状态</x:v>
+        <x:v>Model, prompt version, fact ID, input version, time, and status</x:v>
       </x:c>
       <x:c r="F29" s="5" t="str">
-        <x:v>无凭据仍有 Mock；调用失败可追踪且不泄露原文日志</x:v>
+        <x:v>No credentials still have Mock; call failure is trackable and does not leak original log</x:v>
       </x:c>
       <x:c r="G29" s="5" t="str">
         <x:v>P1-18</x:v>
@@ -1776,10 +1776,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I29" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J29" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K29" s="12" t="str"/>
       <x:c r="L29" s="5" t="str">
@@ -1794,28 +1794,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C30" s="9" t="str">
-        <x:v>工程与验收</x:v>
+        <x:v>Engineering and acceptance</x:v>
       </x:c>
       <x:c r="D30" s="9" t="str">
-        <x:v>Provider 与显式 Mock</x:v>
+        <x:v>Provider and explicit Mock</x:v>
       </x:c>
       <x:c r="E30" s="9" t="str">
-        <x:v>真实搜索/补充/公开搜索/AI 适配；模拟数据隔离</x:v>
+        <x:v>Real search/enrichment/public search/AI adaptation; simulation data isolation</x:v>
       </x:c>
       <x:c r="F30" s="9" t="str">
-        <x:v>真实失败不回退模拟成功；每条模拟结果有标识</x:v>
+        <x:v>Real failure does not roll back simulation success; each simulation result has an identifier</x:v>
       </x:c>
       <x:c r="G30" s="9" t="str">
-        <x:v>P1-09、P1-18</x:v>
+        <x:v>P1-09, P1-18</x:v>
       </x:c>
       <x:c r="H30" s="9" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I30" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J30" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K30" s="12" t="str"/>
       <x:c r="L30" s="9" t="str">
@@ -1830,28 +1830,28 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C31" s="5" t="str">
-        <x:v>工程与验收</x:v>
+        <x:v>Engineering and acceptance</x:v>
       </x:c>
       <x:c r="D31" s="5" t="str">
-        <x:v>Docker 和测试</x:v>
+        <x:v>Docker and testing</x:v>
       </x:c>
       <x:c r="E31" s="5" t="str">
-        <x:v>web/api/db、迁移、种子及关键闭环测试</x:v>
+        <x:v>web/api/db, migration, seed, and key closed-loop testing</x:v>
       </x:c>
       <x:c r="F31" s="5" t="str">
-        <x:v>干净环境依 README 启动；产出实际验证记录</x:v>
+        <x:v>Clean environment starts according to README; actual verification records are produced</x:v>
       </x:c>
       <x:c r="G31" s="5" t="str">
-        <x:v>P1-24、P1-26</x:v>
+        <x:v>P1-24, P1-26</x:v>
       </x:c>
       <x:c r="H31" s="5" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I31" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J31" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K31" s="12" t="str"/>
       <x:c r="L31" s="5" t="str">
@@ -1866,16 +1866,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C32" s="9" t="str">
-        <x:v>账户与邮箱</x:v>
+        <x:v>Account and email</x:v>
       </x:c>
       <x:c r="D32" s="9" t="str">
-        <x:v>Google 平台登录</x:v>
+        <x:v>Google platform login</x:v>
       </x:c>
       <x:c r="E32" s="9" t="str">
-        <x:v>User/Membership/Session；认领本地演示数据走显式迁移</x:v>
+        <x:v>User/Membership/Session; claim local demo data via explicit migration</x:v>
       </x:c>
       <x:c r="F32" s="9" t="str">
-        <x:v>两个用户跨租户请求被拒；生产无演示登录绕过</x:v>
+        <x:v>Cross-tenant requests from two users are rejected; production has no demo login bypass</x:v>
       </x:c>
       <x:c r="G32" s="9" t="str">
         <x:v>P1-03</x:v>
@@ -1884,10 +1884,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I32" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J32" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K32" s="12" t="str"/>
       <x:c r="L32" s="9" t="str">
@@ -1902,16 +1902,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C33" s="5" t="str">
-        <x:v>账户与邮箱</x:v>
+        <x:v>Account and email</x:v>
       </x:c>
       <x:c r="D33" s="5" t="str">
-        <x:v>多 Gmail 授权</x:v>
+        <x:v>Multiple Gmail authorizations</x:v>
       </x:c>
       <x:c r="E33" s="5" t="str">
-        <x:v>平台登录与 Gmail 连接分开；邮箱地址可不同</x:v>
+        <x:v>Platform login and Gmail connection are separate; email address can be different</x:v>
       </x:c>
       <x:c r="F33" s="5" t="str">
-        <x:v>单用户连接两个邮箱；OAuth state 校验</x:v>
+        <x:v>Single user connects to two emails; OAuth state validation</x:v>
       </x:c>
       <x:c r="G33" s="5" t="str">
         <x:v>P2-01</x:v>
@@ -1920,10 +1920,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I33" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J33" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K33" s="12" t="str"/>
       <x:c r="L33" s="5" t="str">
@@ -1938,16 +1938,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C34" s="9" t="str">
-        <x:v>账户与邮箱</x:v>
+        <x:v>Account and email</x:v>
       </x:c>
       <x:c r="D34" s="9" t="str">
-        <x:v>凭据生命周期</x:v>
+        <x:v>Credential lifecycle</x:v>
       </x:c>
       <x:c r="E34" s="9" t="str">
-        <x:v>服务端加密 Token、刷新、断连及重授权</x:v>
+        <x:v>Server-side encryption of Token, refresh, disconnection, and reauthorization</x:v>
       </x:c>
       <x:c r="F34" s="9" t="str">
-        <x:v>前端/日志无 Token；断连停止对应任务</x:v>
+        <x:v>Frontend/logs have no Token; disconnection stops corresponding tasks</x:v>
       </x:c>
       <x:c r="G34" s="9" t="str">
         <x:v>P2-02</x:v>
@@ -1956,10 +1956,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I34" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J34" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K34" s="12" t="str"/>
       <x:c r="L34" s="9" t="str">
@@ -1974,16 +1974,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C35" s="5" t="str">
-        <x:v>账户与邮箱</x:v>
+        <x:v>Account and email</x:v>
       </x:c>
       <x:c r="D35" s="5" t="str">
-        <x:v>发件身份和配置</x:v>
+        <x:v>Sender identity and configuration</x:v>
       </x:c>
       <x:c r="E35" s="5" t="str">
-        <x:v>授权身份、显示名、平台签名、时区、发送窗口</x:v>
+        <x:v>Authorized identity, display name, platform signature, timezone, and send window</x:v>
       </x:c>
       <x:c r="F35" s="5" t="str">
-        <x:v>不得任意伪造 From；时区及签名预览正确</x:v>
+        <x:v>Cannot arbitrarily forge From; timezone and signature preview are correct</x:v>
       </x:c>
       <x:c r="G35" s="5" t="str">
         <x:v>P2-02</x:v>
@@ -1992,10 +1992,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I35" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J35" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K35" s="12" t="str"/>
       <x:c r="L35" s="5" t="str">
@@ -2010,28 +2010,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C36" s="9" t="str">
-        <x:v>发送</x:v>
+        <x:v>Send</x:v>
       </x:c>
       <x:c r="D36" s="9" t="str">
-        <x:v>发送检查与内容快照</x:v>
+        <x:v>Send check and content snapshot</x:v>
       </x:c>
       <x:c r="E36" s="9" t="str">
-        <x:v>收件人、变量、HTML、安全附件、禁止发送列表</x:v>
+        <x:v>Recipients, variables, HTML, secure attachments, and prohibited send list</x:v>
       </x:c>
       <x:c r="F36" s="9" t="str">
-        <x:v>冻结确认内容；后改模板不变更已批准任务</x:v>
+        <x:v>Freeze confirmed content; changing template does not alter approved tasks</x:v>
       </x:c>
       <x:c r="G36" s="9" t="str">
-        <x:v>P1-22、P2-04</x:v>
+        <x:v>P1-22, P2-04</x:v>
       </x:c>
       <x:c r="H36" s="9" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I36" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J36" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K36" s="12" t="str"/>
       <x:c r="L36" s="9" t="str">
@@ -2046,16 +2046,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C37" s="5" t="str">
-        <x:v>发送</x:v>
+        <x:v>Send</x:v>
       </x:c>
       <x:c r="D37" s="5" t="str">
-        <x:v>测试发送</x:v>
+        <x:v>Test send</x:v>
       </x:c>
       <x:c r="E37" s="5" t="str">
-        <x:v>明确测试地址；选择联系人用于变量预览</x:v>
+        <x:v>Clear test address; select contact for variable preview</x:v>
       </x:c>
       <x:c r="F37" s="5" t="str">
-        <x:v>测试事件不更新正式触达数或联系人联系状态</x:v>
+        <x:v>Test event does not update formal reach count or contact connection status</x:v>
       </x:c>
       <x:c r="G37" s="5" t="str">
         <x:v>P2-05</x:v>
@@ -2064,10 +2064,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I37" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J37" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K37" s="12" t="str"/>
       <x:c r="L37" s="5" t="str">
@@ -2082,16 +2082,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C38" s="9" t="str">
-        <x:v>发送</x:v>
+        <x:v>Send</x:v>
       </x:c>
       <x:c r="D38" s="9" t="str">
-        <x:v>单封正式发送</x:v>
+        <x:v>Single formal send</x:v>
       </x:c>
       <x:c r="E38" s="9" t="str">
-        <x:v>用户明确发送；provider 接受后记 sent</x:v>
+        <x:v>User explicitly sends; provider accepts and marks as sent</x:v>
       </x:c>
       <x:c r="F38" s="9" t="str">
-        <x:v>发送返回 ID；不得把 sent 标为已送达/已读</x:v>
+        <x:v>Send returns ID; cannot mark sent as delivered/read</x:v>
       </x:c>
       <x:c r="G38" s="9" t="str">
         <x:v>P2-05</x:v>
@@ -2100,10 +2100,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I38" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J38" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K38" s="12" t="str"/>
       <x:c r="L38" s="9" t="str">
@@ -2118,16 +2118,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C39" s="5" t="str">
-        <x:v>发送</x:v>
+        <x:v>Send</x:v>
       </x:c>
       <x:c r="D39" s="5" t="str">
-        <x:v>单封定时发送</x:v>
+        <x:v>Single scheduled send</x:v>
       </x:c>
       <x:c r="E39" s="5" t="str">
-        <x:v>PostgreSQL 任务+Redis/Worker；合法窗口和限额</x:v>
+        <x:v>PostgreSQL task + Redis/Worker; valid window and limits</x:v>
       </x:c>
       <x:c r="F39" s="5" t="str">
-        <x:v>重启恢复；取消生效；时区/DST 边界有测试</x:v>
+        <x:v>Restart recovery; cancel effective; timezone/DST boundaries have testing</x:v>
       </x:c>
       <x:c r="G39" s="5" t="str">
         <x:v>P2-07</x:v>
@@ -2136,10 +2136,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I39" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J39" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K39" s="12" t="str"/>
       <x:c r="L39" s="5" t="str">
@@ -2154,16 +2154,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C40" s="9" t="str">
-        <x:v>发送</x:v>
+        <x:v>Send</x:v>
       </x:c>
       <x:c r="D40" s="9" t="str">
-        <x:v>幂等与不确定结果</x:v>
+        <x:v>Idempotency and uncertain results</x:v>
       </x:c>
       <x:c r="E40" s="9" t="str">
-        <x:v>独立幂等键和 SendAttempt；超时进入 unknown</x:v>
+        <x:v>Independent idempotency key and SendAttempt; timeout enters unknown</x:v>
       </x:c>
       <x:c r="F40" s="9" t="str">
-        <x:v>重复点击不重复任务；可能已发送不盲目重试</x:v>
+        <x:v>Duplicate click does not duplicate task; may have sent, do not blindly retry</x:v>
       </x:c>
       <x:c r="G40" s="9" t="str">
         <x:v>P2-08</x:v>
@@ -2172,10 +2172,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I40" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J40" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K40" s="12" t="str"/>
       <x:c r="L40" s="9" t="str">
@@ -2190,16 +2190,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C41" s="5" t="str">
-        <x:v>发送</x:v>
+        <x:v>Send</x:v>
       </x:c>
       <x:c r="D41" s="5" t="str">
-        <x:v>附件与发送记录</x:v>
+        <x:v>Attachments and send records</x:v>
       </x:c>
       <x:c r="E41" s="5" t="str">
-        <x:v>用户主动附简历，记录 MIME 大小和结果</x:v>
+        <x:v>User actively attaches resume, record MIME size and result</x:v>
       </x:c>
       <x:c r="F41" s="5" t="str">
-        <x:v>未勾选不附简历；失败可查具体原因</x:v>
+        <x:v>Unselected does not attach resume; failure can check specific cause</x:v>
       </x:c>
       <x:c r="G41" s="5" t="str">
         <x:v>P2-05</x:v>
@@ -2208,10 +2208,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I41" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J41" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K41" s="12" t="str"/>
       <x:c r="L41" s="5" t="str">
@@ -2226,16 +2226,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C42" s="9" t="str">
-        <x:v>发送</x:v>
+        <x:v>Send</x:v>
       </x:c>
       <x:c r="D42" s="9" t="str">
-        <x:v>禁止发送基础</x:v>
+        <x:v>Prohibit sending base</x:v>
       </x:c>
       <x:c r="E42" s="9" t="str">
-        <x:v>用户手动屏蔽地址；工作区跨邮箱执行</x:v>
+        <x:v>User manually blocks an address; workspace cross-email execution</x:v>
       </x:c>
       <x:c r="F42" s="9" t="str">
-        <x:v>屏蔽后待发送任务不会再提交</x:v>
+        <x:v>Tasks to be sent after blocking will no longer be submitted</x:v>
       </x:c>
       <x:c r="G42" s="9" t="str">
         <x:v>P2-08</x:v>
@@ -2244,10 +2244,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I42" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J42" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K42" s="12" t="str"/>
       <x:c r="L42" s="9" t="str">
@@ -2262,28 +2262,28 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C43" s="5" t="str">
-        <x:v>发送</x:v>
+        <x:v>Send</x:v>
       </x:c>
       <x:c r="D43" s="5" t="str">
-        <x:v>双邮箱真实验收</x:v>
+        <x:v>Dual-email real verification</x:v>
       </x:c>
       <x:c r="E43" s="5" t="str">
-        <x:v>指定测试收件人验证真实发送；无凭据标未验证</x:v>
+        <x:v>Specified test recipient verifies real sending; no credential-marked unverified</x:v>
       </x:c>
       <x:c r="F43" s="5" t="str">
-        <x:v>记录邮箱、provider ID和脱敏证据；不联系真实候选人</x:v>
+        <x:v>Record email, provider ID, and masked evidence; no contact with real candidates</x:v>
       </x:c>
       <x:c r="G43" s="5" t="str">
-        <x:v>P2-06、P2-09</x:v>
+        <x:v>P2-06, P2-09</x:v>
       </x:c>
       <x:c r="H43" s="5" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I43" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J43" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K43" s="12" t="str"/>
       <x:c r="L43" s="5" t="str">
@@ -2298,16 +2298,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C44" s="9" t="str">
-        <x:v>收件箱</x:v>
+        <x:v>Inbox</x:v>
       </x:c>
       <x:c r="D44" s="9" t="str">
-        <x:v>首次与增量同步</x:v>
+        <x:v>First sync and incremental sync</x:v>
       </x:c>
       <x:c r="E44" s="9" t="str">
-        <x:v>最近30天、分页、history 游标、轮询及手动刷新</x:v>
+        <x:v>Last 30 days, pagination, history cursor, polling, and manual refresh</x:v>
       </x:c>
       <x:c r="F44" s="9" t="str">
-        <x:v>游标失效可恢复；旧的进行中会话持续跟踪</x:v>
+        <x:v>Cursor invalidation can be recovered; old ongoing sessions continue tracking</x:v>
       </x:c>
       <x:c r="G44" s="9" t="str">
         <x:v>P2-03</x:v>
@@ -2316,10 +2316,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I44" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J44" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K44" s="12" t="str"/>
       <x:c r="L44" s="9" t="str">
@@ -2334,16 +2334,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C45" s="5" t="str">
-        <x:v>收件箱</x:v>
+        <x:v>Inbox</x:v>
       </x:c>
       <x:c r="D45" s="5" t="str">
-        <x:v>会话关联</x:v>
+        <x:v>Session association</x:v>
       </x:c>
       <x:c r="E45" s="5" t="str">
-        <x:v>邮箱+provider ID 唯一；原会话消息头</x:v>
+        <x:v>Email + provider ID unique; original session message header</x:v>
       </x:c>
       <x:c r="F45" s="5" t="str">
-        <x:v>平台外收发也能同步；跨邮箱不误合并</x:v>
+        <x:v>Email sending/receiving outside the platform can be synced; cross-email no mismerge</x:v>
       </x:c>
       <x:c r="G45" s="5" t="str">
         <x:v>P3-01</x:v>
@@ -2352,10 +2352,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I45" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J45" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K45" s="12" t="str"/>
       <x:c r="L45" s="5" t="str">
@@ -2370,16 +2370,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C46" s="9" t="str">
-        <x:v>收件箱</x:v>
+        <x:v>Inbox</x:v>
       </x:c>
       <x:c r="D46" s="9" t="str">
-        <x:v>三栏 Inbox</x:v>
+        <x:v>Three-column Inbox</x:v>
       </x:c>
       <x:c r="E46" s="9" t="str">
-        <x:v>筛选、会话列表、正文与联系人侧栏</x:v>
+        <x:v>Filtering, session list, body, and contact sidebar</x:v>
       </x:c>
       <x:c r="F46" s="9" t="str">
-        <x:v>支持邮箱、领域、未读、待回复；未知领域不默认 Finance</x:v>
+        <x:v>Support email, domain, unread, pending reply; unknown domain not default Finance</x:v>
       </x:c>
       <x:c r="G46" s="9" t="str">
         <x:v>P3-02</x:v>
@@ -2388,10 +2388,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I46" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J46" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K46" s="12" t="str"/>
       <x:c r="L46" s="9" t="str">
@@ -2406,28 +2406,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C47" s="5" t="str">
-        <x:v>收件箱</x:v>
+        <x:v>Inbox</x:v>
       </x:c>
       <x:c r="D47" s="5" t="str">
-        <x:v>原会话回复</x:v>
+        <x:v>Original session reply</x:v>
       </x:c>
       <x:c r="E47" s="5" t="str">
-        <x:v>复用草稿和发送；threadId及回复头</x:v>
+        <x:v>Reuse draft and send; threadId and reply header</x:v>
       </x:c>
       <x:c r="F47" s="5" t="str">
-        <x:v>真实收件端显示在目标会话；不拼成新会话</x:v>
+        <x:v>Real recipient display in target session; no new session created</x:v>
       </x:c>
       <x:c r="G47" s="5" t="str">
-        <x:v>P3-03、P2-07</x:v>
+        <x:v>P3-03, P2-07</x:v>
       </x:c>
       <x:c r="H47" s="5" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I47" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J47" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K47" s="12" t="str"/>
       <x:c r="L47" s="5" t="str">
@@ -2442,16 +2442,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C48" s="9" t="str">
-        <x:v>收件箱</x:v>
+        <x:v>Inbox</x:v>
       </x:c>
       <x:c r="D48" s="9" t="str">
-        <x:v>已读归档与备注</x:v>
+        <x:v>Read archive and notes</x:v>
       </x:c>
       <x:c r="E48" s="9" t="str">
-        <x:v>已读/归档同步 Gmail；意向/备注留平台</x:v>
+        <x:v>Read/archive sync with Gmail; intent/notes remain on platform</x:v>
       </x:c>
       <x:c r="F48" s="9" t="str">
-        <x:v>外部状态和内部字段边界可验证</x:v>
+        <x:v>External status and internal field boundary verifiable</x:v>
       </x:c>
       <x:c r="G48" s="9" t="str">
         <x:v>P3-03</x:v>
@@ -2460,10 +2460,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I48" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J48" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K48" s="12" t="str"/>
       <x:c r="L48" s="9" t="str">
@@ -2478,28 +2478,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C49" s="5" t="str">
-        <x:v>收件箱</x:v>
+        <x:v>Inbox</x:v>
       </x:c>
       <x:c r="D49" s="5" t="str">
-        <x:v>回复保护</x:v>
+        <x:v>Reply protection</x:v>
       </x:c>
       <x:c r="E49" s="5" t="str">
-        <x:v>新回复暂停已有待发任务，区分自动/人工/未知</x:v>
+        <x:v>New reply pauses existing pending tasks, distinguish automatic/manual/unknown</x:v>
       </x:c>
       <x:c r="F49" s="5" t="str">
-        <x:v>暂停有原因；不生成任何下一封；人工确认后可继续</x:v>
+        <x:v>Pause with reason; no next email generated; can resume after manual confirmation</x:v>
       </x:c>
       <x:c r="G49" s="5" t="str">
-        <x:v>P3-02、P2-08</x:v>
+        <x:v>P3-02, P2-08</x:v>
       </x:c>
       <x:c r="H49" s="5" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I49" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J49" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K49" s="12" t="str"/>
       <x:c r="L49" s="5" t="str">
@@ -2514,28 +2514,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C50" s="9" t="str">
-        <x:v>收件箱</x:v>
+        <x:v>Inbox</x:v>
       </x:c>
       <x:c r="D50" s="9" t="str">
-        <x:v>退信拒绝和退订</x:v>
+        <x:v>Bounce rejection and unsubscribe</x:v>
       </x:c>
       <x:c r="E50" s="9" t="str">
-        <x:v>地址级硬退信及工作区 suppression；退订入口</x:v>
+        <x:v>Address-level hard bounce and workspace suppression; unsubscribe entry</x:v>
       </x:c>
       <x:c r="F50" s="9" t="str">
-        <x:v>同工作区换邮箱仍受限；不把模糊自然语言当准确判定</x:v>
+        <x:v>Same workspace change email still restricted; do not treat ambiguous natural language as accurate judgment</x:v>
       </x:c>
       <x:c r="G50" s="9" t="str">
-        <x:v>P3-02、P2-11</x:v>
+        <x:v>P3-02, P2-11</x:v>
       </x:c>
       <x:c r="H50" s="9" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I50" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J50" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K50" s="12" t="str"/>
       <x:c r="L50" s="9" t="str">
@@ -2550,16 +2550,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C51" s="5" t="str">
-        <x:v>手动跟进</x:v>
+        <x:v>Manual Follow-Up</x:v>
       </x:c>
       <x:c r="D51" s="5" t="str">
-        <x:v>跟进任务</x:v>
+        <x:v>Follow-up task</x:v>
       </x:c>
       <x:c r="E51" s="5" t="str">
-        <x:v>联系人/会话、时间、备注、完成/改期/取消</x:v>
+        <x:v>Contact/session, time, note, complete/reschedule/cancel</x:v>
       </x:c>
       <x:c r="F51" s="5" t="str">
-        <x:v>到期只在平台提醒，不发邮件</x:v>
+        <x:v>Expiration only reminds on platform, no email sent</x:v>
       </x:c>
       <x:c r="G51" s="5" t="str">
         <x:v>P3-03</x:v>
@@ -2568,10 +2568,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I51" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J51" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K51" s="12" t="str"/>
       <x:c r="L51" s="5" t="str">
@@ -2586,28 +2586,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C52" s="9" t="str">
-        <x:v>手动跟进</x:v>
+        <x:v>Manual Follow-Up</x:v>
       </x:c>
       <x:c r="D52" s="9" t="str">
-        <x:v>主动跟进写作</x:v>
+        <x:v>Proactive follow-up writing</x:v>
       </x:c>
       <x:c r="E52" s="9" t="str">
-        <x:v>用户点击任务进入原会话，选择模板/AI，再确认发送</x:v>
+        <x:v>User clicks task to enter original session, selects template/AI, then confirms send</x:v>
       </x:c>
       <x:c r="F52" s="9" t="str">
-        <x:v>必须有用户动作；不会由到期事件自动排期</x:v>
+        <x:v>Must have user action; no auto-scheduling by expiration event</x:v>
       </x:c>
       <x:c r="G52" s="9" t="str">
-        <x:v>P3-08、P3-04</x:v>
+        <x:v>P3-08, P3-04</x:v>
       </x:c>
       <x:c r="H52" s="9" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I52" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J52" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K52" s="12" t="str"/>
       <x:c r="L52" s="9" t="str">
@@ -2622,16 +2622,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C53" s="5" t="str">
-        <x:v>手动跟进</x:v>
+        <x:v>Manual Follow-Up</x:v>
       </x:c>
       <x:c r="D53" s="5" t="str">
-        <x:v>同步异常可见</x:v>
+        <x:v>Sync anomalies visible</x:v>
       </x:c>
       <x:c r="E53" s="5" t="str">
-        <x:v>最后同步时间、断连、限流和失败提示</x:v>
+        <x:v>Last sync time, disconnection, rate limit, and failure prompt</x:v>
       </x:c>
       <x:c r="F53" s="5" t="str">
-        <x:v>同步失败暂停相关未发跟进草稿排期检查</x:v>
+        <x:v>Sync failure pauses related unsent follow-up draft scheduling check</x:v>
       </x:c>
       <x:c r="G53" s="5" t="str">
         <x:v>P3-01</x:v>
@@ -2640,10 +2640,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I53" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J53" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K53" s="12" t="str"/>
       <x:c r="L53" s="5" t="str">
@@ -2658,28 +2658,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C54" s="9" t="str">
-        <x:v>手动跟进</x:v>
+        <x:v>Manual Follow-Up</x:v>
       </x:c>
       <x:c r="D54" s="9" t="str">
-        <x:v>回复闭环验收</x:v>
+        <x:v>Reply loop closure verification</x:v>
       </x:c>
       <x:c r="E54" s="9" t="str">
-        <x:v>指定邮箱真实回复和未知状态样例</x:v>
+        <x:v>Specified email real reply and unknown status sample</x:v>
       </x:c>
       <x:c r="F54" s="9" t="str">
-        <x:v>收件端回复到 Inbox；已排期消息受保护</x:v>
+        <x:v>Recipient reply to Inbox; scheduled messages protected</x:v>
       </x:c>
       <x:c r="G54" s="9" t="str">
-        <x:v>P3-06、P3-09</x:v>
+        <x:v>P3-06, P3-09</x:v>
       </x:c>
       <x:c r="H54" s="9" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I54" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J54" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K54" s="12" t="str"/>
       <x:c r="L54" s="9" t="str">
@@ -2694,16 +2694,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C55" s="5" t="str">
-        <x:v>批量与完善</x:v>
+        <x:v>Batch and refinement</x:v>
       </x:c>
       <x:c r="D55" s="5" t="str">
-        <x:v>模板和 Snippet 管理</x:v>
+        <x:v>Template and Snippet management</x:v>
       </x:c>
       <x:c r="E55" s="5" t="str">
-        <x:v>分类、创建/编辑、版本；Academic 示例标记</x:v>
+        <x:v>Categorization, create/edit, version; Academic example marking</x:v>
       </x:c>
       <x:c r="F55" s="5" t="str">
-        <x:v>旧的已批准邮件不随模板变化</x:v>
+        <x:v>Previously approved emails not change with template</x:v>
       </x:c>
       <x:c r="G55" s="5" t="str">
         <x:v>P1-24</x:v>
@@ -2712,10 +2712,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I55" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J55" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K55" s="12" t="str"/>
       <x:c r="L55" s="5" t="str">
@@ -2730,28 +2730,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C56" s="9" t="str">
-        <x:v>批量与完善</x:v>
+        <x:v>Batch and refinement</x:v>
       </x:c>
       <x:c r="D56" s="9" t="str">
-        <x:v>批量活动</x:v>
+        <x:v>Batch activity</x:v>
       </x:c>
       <x:c r="E56" s="9" t="str">
-        <x:v>名单、逐人内容、邮箱、时间和用户批准记录</x:v>
+        <x:v>List, per-person content, email, time, and user approval record</x:v>
       </x:c>
       <x:c r="F56" s="9" t="str">
-        <x:v>Campaign 无步骤/自动序列；逐人独立 To</x:v>
+        <x:v>Campaign no steps/automated email sequence; per-person independent To</x:v>
       </x:c>
       <x:c r="G56" s="9" t="str">
-        <x:v>P2-09、P3-06</x:v>
+        <x:v>P2-09, P3-06</x:v>
       </x:c>
       <x:c r="H56" s="9" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I56" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J56" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K56" s="12" t="str"/>
       <x:c r="L56" s="9" t="str">
@@ -2766,16 +2766,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C57" s="5" t="str">
-        <x:v>批量与完善</x:v>
+        <x:v>Batch and refinement</x:v>
       </x:c>
       <x:c r="D57" s="5" t="str">
-        <x:v>批量预检</x:v>
+        <x:v>Batch pre-check</x:v>
       </x:c>
       <x:c r="E57" s="5" t="str">
-        <x:v>变量、重复、邮箱、屏蔽、附件与窗口汇总</x:v>
+        <x:v>Variables, repetition, email, block, attachment, and window summary</x:v>
       </x:c>
       <x:c r="F57" s="5" t="str">
-        <x:v>异常联系人可明确排除；不静默跳过</x:v>
+        <x:v>Abnormal contacts can be clearly excluded; no silent skip</x:v>
       </x:c>
       <x:c r="G57" s="5" t="str">
         <x:v>P4-02</x:v>
@@ -2784,10 +2784,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I57" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J57" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K57" s="12" t="str"/>
       <x:c r="L57" s="5" t="str">
@@ -2802,16 +2802,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C58" s="9" t="str">
-        <x:v>批量与完善</x:v>
+        <x:v>Batch and refinement</x:v>
       </x:c>
       <x:c r="D58" s="9" t="str">
-        <x:v>活动控制</x:v>
+        <x:v>Activity control</x:v>
       </x:c>
       <x:c r="E58" s="9" t="str">
-        <x:v>暂停/恢复/终止、单人退出、进度</x:v>
+        <x:v>Pause/resume/terminate, single-person exit, progress</x:v>
       </x:c>
       <x:c r="F58" s="9" t="str">
-        <x:v>恢复重算窗口；不瞬间补发；重复启动不重复发</x:v>
+        <x:v>Resume recalculation window; no instant resend; no duplicate send on repeated start</x:v>
       </x:c>
       <x:c r="G58" s="9" t="str">
         <x:v>P4-03</x:v>
@@ -2820,10 +2820,10 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I58" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J58" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K58" s="12" t="str"/>
       <x:c r="L58" s="9" t="str">
@@ -2838,28 +2838,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C59" s="5" t="str">
-        <x:v>批量与完善</x:v>
+        <x:v>Batch and refinement</x:v>
       </x:c>
       <x:c r="D59" s="5" t="str">
-        <x:v>基础 Analytics</x:v>
+        <x:v>Basic Analytics</x:v>
       </x:c>
       <x:c r="E59" s="5" t="str">
-        <x:v>正式发送邮件数/人数、人工回复、退信、退订</x:v>
+        <x:v>Number of formal sent emails/persons, manual replies, bounces, unsubscribes</x:v>
       </x:c>
       <x:c r="F59" s="5" t="str">
-        <x:v>分母、时间、去重有说明；测试和Mock分开</x:v>
+        <x:v>Denominator, time, deduplication with explanation; test and Mock separated</x:v>
       </x:c>
       <x:c r="G59" s="5" t="str">
-        <x:v>P4-02、P3-07</x:v>
+        <x:v>P4-02, P3-07</x:v>
       </x:c>
       <x:c r="H59" s="5" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I59" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J59" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K59" s="12" t="str"/>
       <x:c r="L59" s="5" t="str">
@@ -2874,28 +2874,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C60" s="9" t="str">
-        <x:v>批量与完善</x:v>
+        <x:v>Batch and refinement</x:v>
       </x:c>
       <x:c r="D60" s="9" t="str">
-        <x:v>设置与维护</x:v>
+        <x:v>Settings and maintenance</x:v>
       </x:c>
       <x:c r="E60" s="9" t="str">
-        <x:v>整合画像、邮箱和 AI 配置；导出/删除受控数据</x:v>
+        <x:v>Integrate persona, email, and AI configuration; export/delete controlled data</x:v>
       </x:c>
       <x:c r="F60" s="9" t="str">
-        <x:v>不展示密钥；删除与保留 suppression 的含义明确</x:v>
+        <x:v>No key display; deletion and retention of suppression meaning clear</x:v>
       </x:c>
       <x:c r="G60" s="9" t="str">
-        <x:v>P2-01、P4-05</x:v>
+        <x:v>P2-01, P4-05</x:v>
       </x:c>
       <x:c r="H60" s="9" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I60" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J60" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K60" s="12" t="str"/>
       <x:c r="L60" s="9" t="str">
@@ -2910,28 +2910,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C61" s="5" t="str">
-        <x:v>批量与完善</x:v>
+        <x:v>Batch and refinement</x:v>
       </x:c>
       <x:c r="D61" s="5" t="str">
-        <x:v>Academic 契约</x:v>
+        <x:v>Academic Contract</x:v>
       </x:c>
       <x:c r="E61" s="5" t="str">
-        <x:v>Persona/Mentor 结构、Provider 搜索/详情/分页/错误契约</x:v>
+        <x:v>Persona/Mentor structure, Provider search/detail/pagination/error contract</x:v>
       </x:c>
       <x:c r="F61" s="5" t="str">
-        <x:v>JSONL/SQLite/Postgres/External 仅骨架；返回未实现</x:v>
+        <x:v>JSONL/SQLite/Postgres/External only skeleton; return not implemented</x:v>
       </x:c>
       <x:c r="G61" s="5" t="str">
-        <x:v>P1-05、P1-15</x:v>
+        <x:v>P1-05, P1-15</x:v>
       </x:c>
       <x:c r="H61" s="5" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I61" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J61" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K61" s="12" t="str"/>
       <x:c r="L61" s="5" t="str">
@@ -2946,28 +2946,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C62" s="9" t="str">
-        <x:v>批量与完善</x:v>
+        <x:v>Batch and refinement</x:v>
       </x:c>
       <x:c r="D62" s="9" t="str">
-        <x:v>整体回归与上线清单</x:v>
+        <x:v>Overall regression and release checklist</x:v>
       </x:c>
       <x:c r="E62" s="9" t="str">
-        <x:v>验证四期功能；外部审核、备份、监控单独标记</x:v>
+        <x:v>Verify four-phase features; external review, backup, monitoring marked separately</x:v>
       </x:c>
       <x:c r="F62" s="9" t="str">
-        <x:v>不得将文档/演示制作完成写成产品开发完成</x:v>
+        <x:v>Do not write document/demo completion as product development completion</x:v>
       </x:c>
       <x:c r="G62" s="9" t="str">
-        <x:v>P4-01至P4-07</x:v>
+        <x:v>P4-01 to P4-07</x:v>
       </x:c>
       <x:c r="H62" s="9" t="str">
         <x:v>Must</x:v>
       </x:c>
       <x:c r="I62" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J62" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K62" s="12" t="str"/>
       <x:c r="L62" s="9" t="str">
@@ -2982,32 +2982,32 @@
         <x:v>Soon</x:v>
       </x:c>
       <x:c r="C63" s="5" t="str">
-        <x:v>管理员后端</x:v>
+        <x:v>Admin backend</x:v>
       </x:c>
       <x:c r="D63" s="5" t="str">
-        <x:v>运行概览</x:v>
+        <x:v>Overview of operation</x:v>
       </x:c>
       <x:c r="E63" s="5" t="str">
-        <x:v>用户、邮箱故障、排队和失败任务汇总，支持下钻</x:v>
+        <x:v>Summary of users, email failures, queued and failed tasks, supports drilling down</x:v>
       </x:c>
       <x:c r="F63" s="5" t="str">
-        <x:v>汇总可追溯原始事件，空数据不伪造健康指标</x:v>
+        <x:v>Aggregate traceable to the original event, no fake health metrics for empty data</x:v>
       </x:c>
       <x:c r="G63" s="5" t="str">
-        <x:v>正式账户与平台角色；对应业务模块已实现</x:v>
+        <x:v>Formal account and platform roles; corresponding business modules implemented</x:v>
       </x:c>
       <x:c r="H63" s="5" t="str">
         <x:v>Should</x:v>
       </x:c>
       <x:c r="I63" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J63" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K63" s="12" t="str"/>
       <x:c r="L63" s="5" t="str">
-        <x:v>Soon 待定</x:v>
+        <x:v>Soon pending</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="64" customHeight="1">
@@ -3018,32 +3018,32 @@
         <x:v>Soon</x:v>
       </x:c>
       <x:c r="C64" s="9" t="str">
-        <x:v>管理员后端</x:v>
+        <x:v>Admin backend</x:v>
       </x:c>
       <x:c r="D64" s="9" t="str">
-        <x:v>用户管理</x:v>
+        <x:v>User management</x:v>
       </x:c>
       <x:c r="E64" s="9" t="str">
-        <x:v>查询账户与工作区状态，停用和恢复账户</x:v>
+        <x:v>Query account and workspace status, disable and re-enable account</x:v>
       </x:c>
       <x:c r="F64" s="9" t="str">
-        <x:v>停用阻止新发送；恢复不自动恢复已暂停任务</x:v>
+        <x:v>Disable to prevent new sends; restore does not automatically resume paused tasks</x:v>
       </x:c>
       <x:c r="G64" s="9" t="str">
-        <x:v>正式账户与平台角色；对应业务模块已实现</x:v>
+        <x:v>Formal account and platform roles; corresponding business modules implemented</x:v>
       </x:c>
       <x:c r="H64" s="9" t="str">
         <x:v>Should</x:v>
       </x:c>
       <x:c r="I64" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J64" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K64" s="12" t="str"/>
       <x:c r="L64" s="9" t="str">
-        <x:v>Soon 待定</x:v>
+        <x:v>Soon pending</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="64" customHeight="1">
@@ -3054,32 +3054,32 @@
         <x:v>Soon</x:v>
       </x:c>
       <x:c r="C65" s="5" t="str">
-        <x:v>管理员后端</x:v>
+        <x:v>Admin backend</x:v>
       </x:c>
       <x:c r="D65" s="5" t="str">
-        <x:v>邮箱连接</x:v>
+        <x:v>Email connection</x:v>
       </x:c>
       <x:c r="E65" s="5" t="str">
-        <x:v>查看归属、授权状态、同步错误；暂停相关任务</x:v>
+        <x:v>View ownership, authorization status, sync errors; pause related tasks</x:v>
       </x:c>
       <x:c r="F65" s="5" t="str">
-        <x:v>不显示 Token；重新授权由邮箱所有者完成</x:v>
+        <x:v>Do not display Token; reauthorization is completed by the email owner</x:v>
       </x:c>
       <x:c r="G65" s="5" t="str">
-        <x:v>正式账户与平台角色；对应业务模块已实现</x:v>
+        <x:v>Formal account and platform roles; corresponding business modules implemented</x:v>
       </x:c>
       <x:c r="H65" s="5" t="str">
         <x:v>Should</x:v>
       </x:c>
       <x:c r="I65" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J65" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K65" s="12" t="str"/>
       <x:c r="L65" s="5" t="str">
-        <x:v>Soon 待定</x:v>
+        <x:v>Soon pending</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="64" customHeight="1">
@@ -3090,32 +3090,32 @@
         <x:v>Soon</x:v>
       </x:c>
       <x:c r="C66" s="9" t="str">
-        <x:v>管理员后端</x:v>
+        <x:v>Admin backend</x:v>
       </x:c>
       <x:c r="D66" s="9" t="str">
-        <x:v>发送任务</x:v>
+        <x:v>Send task</x:v>
       </x:c>
       <x:c r="E66" s="9" t="str">
-        <x:v>筛选排队、定时、失败与 unknown 任务；暂停和取消</x:v>
+        <x:v>Filter queued, scheduled, failed and unknown tasks; pause and cancel</x:v>
       </x:c>
       <x:c r="F66" s="9" t="str">
-        <x:v>unknown 先核对结果，不提供盲目重发</x:v>
+        <x:v>unknown: verify results first, do not provide blind resends</x:v>
       </x:c>
       <x:c r="G66" s="9" t="str">
-        <x:v>正式账户与平台角色；对应业务模块已实现</x:v>
+        <x:v>Formal account and platform roles; corresponding business modules implemented</x:v>
       </x:c>
       <x:c r="H66" s="9" t="str">
         <x:v>Should</x:v>
       </x:c>
       <x:c r="I66" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J66" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K66" s="12" t="str"/>
       <x:c r="L66" s="9" t="str">
-        <x:v>Soon 待定</x:v>
+        <x:v>Soon pending</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="64" customHeight="1">
@@ -3126,32 +3126,32 @@
         <x:v>Soon</x:v>
       </x:c>
       <x:c r="C67" s="5" t="str">
-        <x:v>管理员后端</x:v>
+        <x:v>Admin backend</x:v>
       </x:c>
       <x:c r="D67" s="5" t="str">
-        <x:v>服务与 AI 配置</x:v>
+        <x:v>Service and AI configuration</x:v>
       </x:c>
       <x:c r="E67" s="5" t="str">
-        <x:v>管理提供商连接、模型、额度、超时及重试参数</x:v>
+        <x:v>Manage provider connections, models, quotas, timeouts and retry parameters</x:v>
       </x:c>
       <x:c r="F67" s="5" t="str">
-        <x:v>密钥只写不回显，变更可审计</x:v>
+        <x:v>Key is written only, not echoed back; changes are auditable</x:v>
       </x:c>
       <x:c r="G67" s="5" t="str">
-        <x:v>正式账户与平台角色；对应业务模块已实现</x:v>
+        <x:v>Formal account and platform roles; corresponding business modules implemented</x:v>
       </x:c>
       <x:c r="H67" s="5" t="str">
         <x:v>Should</x:v>
       </x:c>
       <x:c r="I67" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J67" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K67" s="12" t="str"/>
       <x:c r="L67" s="5" t="str">
-        <x:v>Soon 待定</x:v>
+        <x:v>Soon pending</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="64" customHeight="1">
@@ -3162,32 +3162,32 @@
         <x:v>Soon</x:v>
       </x:c>
       <x:c r="C68" s="9" t="str">
-        <x:v>管理员后端</x:v>
+        <x:v>Admin backend</x:v>
       </x:c>
       <x:c r="D68" s="9" t="str">
-        <x:v>同步任务</x:v>
+        <x:v>Synchronization task</x:v>
       </x:c>
       <x:c r="E68" s="9" t="str">
-        <x:v>查看同步游标、延迟与错误，执行受控恢复</x:v>
+        <x:v>View sync cursor, delay and errors, execute controlled recovery</x:v>
       </x:c>
       <x:c r="F68" s="9" t="str">
-        <x:v>恢复保留去重和会话关联，不制造重复消息</x:v>
+        <x:v>Restore preserves deduplication and session association, does not create duplicate messages</x:v>
       </x:c>
       <x:c r="G68" s="9" t="str">
-        <x:v>正式账户与平台角色；对应业务模块已实现</x:v>
+        <x:v>Formal account and platform roles; corresponding business modules implemented</x:v>
       </x:c>
       <x:c r="H68" s="9" t="str">
         <x:v>Should</x:v>
       </x:c>
       <x:c r="I68" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J68" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K68" s="12" t="str"/>
       <x:c r="L68" s="9" t="str">
-        <x:v>Soon 待定</x:v>
+        <x:v>Soon pending</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="64" customHeight="1">
@@ -3198,32 +3198,32 @@
         <x:v>Soon</x:v>
       </x:c>
       <x:c r="C69" s="5" t="str">
-        <x:v>管理员后端</x:v>
+        <x:v>Admin backend</x:v>
       </x:c>
       <x:c r="D69" s="5" t="str">
-        <x:v>平台模板与提示词</x:v>
+        <x:v>Platform templates and prompts</x:v>
       </x:c>
       <x:c r="E69" s="5" t="str">
-        <x:v>测试、发布和回滚平台模板及 AI 提示词版本</x:v>
+        <x:v>Test, publish and rollback platform templates and AI prompt versions</x:v>
       </x:c>
       <x:c r="F69" s="5" t="str">
-        <x:v>新版本不改变已批准邮件的内容快照</x:v>
+        <x:v>New version does not change the content snapshot of approved emails</x:v>
       </x:c>
       <x:c r="G69" s="5" t="str">
-        <x:v>正式账户与平台角色；对应业务模块已实现</x:v>
+        <x:v>Formal account and platform roles; corresponding business modules implemented</x:v>
       </x:c>
       <x:c r="H69" s="5" t="str">
         <x:v>Should</x:v>
       </x:c>
       <x:c r="I69" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J69" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K69" s="12" t="str"/>
       <x:c r="L69" s="5" t="str">
-        <x:v>Soon 待定</x:v>
+        <x:v>Soon pending</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="64" customHeight="1">
@@ -3234,32 +3234,32 @@
         <x:v>Soon</x:v>
       </x:c>
       <x:c r="C70" s="9" t="str">
-        <x:v>管理员后端</x:v>
+        <x:v>Admin backend</x:v>
       </x:c>
       <x:c r="D70" s="9" t="str">
-        <x:v>用量与成本</x:v>
+        <x:v>Usage and cost</x:v>
       </x:c>
       <x:c r="E70" s="9" t="str">
-        <x:v>按用户、日期及提供商查看调用量和成本</x:v>
+        <x:v>View usage and cost by user, date and provider</x:v>
       </x:c>
       <x:c r="F70" s="9" t="str">
-        <x:v>实测用量、估算成本和账单分别标明</x:v>
+        <x:v>Measured usage, estimated cost, and billing are separately indicated</x:v>
       </x:c>
       <x:c r="G70" s="9" t="str">
-        <x:v>正式账户与平台角色；对应业务模块已实现</x:v>
+        <x:v>Formal account and platform roles; corresponding business modules implemented</x:v>
       </x:c>
       <x:c r="H70" s="9" t="str">
         <x:v>Should</x:v>
       </x:c>
       <x:c r="I70" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J70" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K70" s="12" t="str"/>
       <x:c r="L70" s="9" t="str">
-        <x:v>Soon 待定</x:v>
+        <x:v>Soon pending</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="64" customHeight="1">
@@ -3270,38 +3270,38 @@
         <x:v>Soon</x:v>
       </x:c>
       <x:c r="C71" s="5" t="str">
-        <x:v>管理员后端</x:v>
+        <x:v>Admin backend</x:v>
       </x:c>
       <x:c r="D71" s="5" t="str">
-        <x:v>审计与平台设置</x:v>
+        <x:v>Audit and platform settings</x:v>
       </x:c>
       <x:c r="E71" s="5" t="str">
-        <x:v>查询管理操作日志，管理默认限制与功能开关</x:v>
+        <x:v>Query management operation logs, manage default limits and feature switches</x:v>
       </x:c>
       <x:c r="F71" s="5" t="str">
-        <x:v>服务端校验平台管理员身份；操作记录操作者、时间和原因</x:v>
+        <x:v>Server-side verification of platform admin identity; operation records include operator, time, and reason</x:v>
       </x:c>
       <x:c r="G71" s="5" t="str">
-        <x:v>正式账户与平台角色；对应业务模块已实现</x:v>
+        <x:v>Formal account and platform roles; corresponding business modules implemented</x:v>
       </x:c>
       <x:c r="H71" s="5" t="str">
         <x:v>Should</x:v>
       </x:c>
       <x:c r="I71" s="12" t="str">
-        <x:v>未开始</x:v>
+        <x:v>Not started</x:v>
       </x:c>
       <x:c r="J71" s="12" t="str">
-        <x:v>未验证</x:v>
+        <x:v>Unverified</x:v>
       </x:c>
       <x:c r="K71" s="12" t="str"/>
       <x:c r="L71" s="5" t="str">
-        <x:v>Soon 待定</x:v>
+        <x:v>Soon pending</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="I5:I71">
-    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="已完成"/>
-    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="阻塞"/>
+    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Completed"/>
+    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Blocked"/>
   </x:conditionalFormatting>
   <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="B5:B71">
@@ -3311,15 +3311,15 @@
       <x:formula1>"Must,Should,Could"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="I5:I71">
-      <x:formula1>"未开始,开发中,已完成,阻塞"</x:formula1>
+      <x:formula1>"Not started,In Development,Completed,Blocked"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="J5:J71">
-      <x:formula1>"未验证,Mock验证,真实验证,不适用"</x:formula1>
+      <x:formula1>"Unverified,Mock Verification,Real Verification,Not Applicable"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R771fd1f626f64c99"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R524b49f0f50248f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3338,7 +3338,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="2" t="str">
-        <x:v>AI写作交互与状态</x:v>
+        <x:v>AI Writing Interaction and Status</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -3348,7 +3348,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>输入、用户动作、输出和需求ID对应详细设计第03至07节。</x:v>
+        <x:v>Input, user actions, output, and requirement ID correspond to detailed design sections 03 to 07</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -3366,22 +3366,22 @@
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="8" t="str">
-        <x:v>步骤ID</x:v>
+        <x:v>Step ID</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
-        <x:v>交互</x:v>
+        <x:v>Interaction</x:v>
       </x:c>
       <x:c r="C4" s="8" t="str">
-        <x:v>输入</x:v>
+        <x:v>Input</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
-        <x:v>动作与规则</x:v>
+        <x:v>Actions and Rules</x:v>
       </x:c>
       <x:c r="E4" s="8" t="str">
-        <x:v>输出</x:v>
+        <x:v>Output</x:v>
       </x:c>
       <x:c r="F4" s="8" t="str">
-        <x:v>需求ID</x:v>
+        <x:v>Requirement ID</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
@@ -3389,16 +3389,16 @@
         <x:v>W01</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>设置 Brief</x:v>
+        <x:v>Settings Brief</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>Persona 版本、联系人、目的、CTA、语气、语言、长度</x:v>
+        <x:v>Persona Version, Contact, Purpose, CTA, Tone, Language, Length</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>保存写作意图，未选画像仍可手写</x:v>
+        <x:v>Save writing intent, can manually write even without a persona selected</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>可生成或待补充背景</x:v>
+        <x:v>Can generate or pending background</x:v>
       </x:c>
       <x:c r="F5" s="5" t="str">
         <x:v>P1-16</x:v>
@@ -3409,16 +3409,16 @@
         <x:v>W02</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>挑选证据</x:v>
+        <x:v>Select Evidence</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>confirmed / inferred / unknown / conflict；fact_id、来源</x:v>
+        <x:v>confirmed / inferred / unknown / conflict; fact_id, source</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>默认仅建议 confirmed；用户可取消事实</x:v>
+        <x:v>Default only suggests confirmed; users can deselect facts</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
-        <x:v>allowed_fact_ids 与待确认事实</x:v>
+        <x:v>allowed_fact_ids and pending facts</x:v>
       </x:c>
       <x:c r="F6" s="9" t="str">
         <x:v>P1-17</x:v>
@@ -3429,16 +3429,16 @@
         <x:v>W03</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>生成建议</x:v>
+        <x:v>Generation suggestions</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>Brief + 允许事实 + 当前 revision</x:v>
+        <x:v>Brief + allowed facts + current revision</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>模型返回建议；不替换正文</x:v>
+        <x:v>Model returns suggestions; do not replace the body</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>subject、body_blocks、claims、warnings</x:v>
+        <x:v>subject, body_blocks, claims, warnings</x:v>
       </x:c>
       <x:c r="F7" s="5" t="str">
         <x:v>P1-18</x:v>
@@ -3449,16 +3449,16 @@
         <x:v>W04</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>检查内容</x:v>
+        <x:v>Check Content</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>结构化输出、变量及引用</x:v>
+        <x:v>Structured Output, Variables, and References</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>确定性字段检查+模型辅助审阅；人工最终判断</x:v>
+        <x:v>Deterministic field check + model-assisted review; final human judgment</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>缺失、无来源陈述、长度建议</x:v>
+        <x:v>Missing variables, unsupported claims, and length suggestions</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
         <x:v>P1-18</x:v>
@@ -3469,16 +3469,16 @@
         <x:v>W05</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>采纳或丢弃</x:v>
+        <x:v>Adopt or discard</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>当前稿和建议稿</x:v>
+        <x:v>Current draft and suggested draft</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>全文比较；采纳新 revision；可撤销</x:v>
+        <x:v>Full comparison; adopt new revision; revocable</x:v>
       </x:c>
       <x:c r="E9" s="5" t="str">
-        <x:v>新稿或保留原稿</x:v>
+        <x:v>New draft or retain original draft</x:v>
       </x:c>
       <x:c r="F9" s="5" t="str">
         <x:v>P1-19</x:v>
@@ -3489,16 +3489,16 @@
         <x:v>W06</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>局部改写</x:v>
+        <x:v>Partial rewriting</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>选区、base_revision、允许事实</x:v>
+        <x:v>Selection, base_revision, allowed facts</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>缩短/语气调整；无选区提示，不覆盖全文</x:v>
+        <x:v>Shorten/adjust tone; no selection prompt, do not overwrite full text</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>候选替换片段</x:v>
+        <x:v>Candidate replacement fragments</x:v>
       </x:c>
       <x:c r="F10" s="9" t="str">
         <x:v>P1-20</x:v>
@@ -3509,19 +3509,19 @@
         <x:v>W07</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>版本冲突</x:v>
+        <x:v>Version conflict</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
-        <x:v>新编辑产生不同 revision</x:v>
+        <x:v>New edits produce different revision</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
-        <x:v>旧建议保持可读但禁用直接应用；重新生成</x:v>
+        <x:v>Old suggestions remain readable but disabled for direct application; regenerate</x:v>
       </x:c>
       <x:c r="E11" s="5" t="str">
-        <x:v>不会丢失人工编辑</x:v>
+        <x:v>No loss of manual edits</x:v>
       </x:c>
       <x:c r="F11" s="5" t="str">
-        <x:v>P1-20、P1-23</x:v>
+        <x:v>P1-20, P1-23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="64" customHeight="1">
@@ -3529,16 +3529,16 @@
         <x:v>W08</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>变量预览</x:v>
+        <x:v>Variable preview</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>模板节点+联系人快照+用户字段</x:v>
+        <x:v>Template node + contact snapshot + user fields</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>必填无值阻止 Ready；默认值须明确</x:v>
+        <x:v>Required fields without value block Ready; default values must be explicit</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>最终主题/正文+missing_variables</x:v>
+        <x:v>Final subject/body + missing variables</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
         <x:v>P1-22</x:v>
@@ -3549,13 +3549,13 @@
         <x:v>W09</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>保存恢复</x:v>
+        <x:v>Save and restore</x:v>
       </x:c>
       <x:c r="C13" s="5" t="str">
-        <x:v>editor_json、plain_text、revision</x:v>
+        <x:v>editor_json, plain_text, revision</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
-        <x:v>防抖保存；失败可重试，409 保留两份</x:v>
+        <x:v>Debounce save; failure can retry, 409 retain two copies</x:v>
       </x:c>
       <x:c r="E13" s="5" t="str">
         <x:v>Saved/Unsaved/Conflict</x:v>
@@ -3569,16 +3569,16 @@
         <x:v>W10</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>正式批准</x:v>
+        <x:v>Formal approval</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
-        <x:v>二期邮件身份和内容快照</x:v>
+        <x:v>Phase two email identity and content snapshot</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>预检并明确批准；后改稿不影响快照</x:v>
+        <x:v>Pre-approval and clear approval; later edits do not affect snapshot</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
-        <x:v>SendJob 或定时任务</x:v>
+        <x:v>SendJob or scheduled task</x:v>
       </x:c>
       <x:c r="F14" s="9" t="str">
         <x:v>P2-05</x:v>
@@ -3589,16 +3589,16 @@
         <x:v>W11</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>人工跟进</x:v>
+        <x:v>Manual follow-up</x:v>
       </x:c>
       <x:c r="C15" s="5" t="str">
-        <x:v>三期原会话和任务</x:v>
+        <x:v>Phase three original conversation and task</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
-        <x:v>到期提醒；人点击后才写下一封</x:v>
+        <x:v>Reminder on expiration; user clicks before writing one email</x:v>
       </x:c>
       <x:c r="E15" s="5" t="str">
-        <x:v>新的人工草稿</x:v>
+        <x:v>New manual draft</x:v>
       </x:c>
       <x:c r="F15" s="5" t="str">
         <x:v>P3-09</x:v>
@@ -3609,16 +3609,16 @@
         <x:v>W12</x:v>
       </x:c>
       <x:c r="B16" s="9" t="str">
-        <x:v>批量逐人审阅</x:v>
+        <x:v>Batch individual review</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>四期联系人集合及逐人事实</x:v>
+        <x:v>Phase four contact set and individual facts</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>限定并发；逐人审阅和异常排除</x:v>
+        <x:v>Limit concurrency; individual review and anomaly exclusion</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
-        <x:v>逐人内容快照</x:v>
+        <x:v>Individual content snapshot</x:v>
       </x:c>
       <x:c r="F16" s="9" t="str">
         <x:v>P4-03</x:v>
@@ -3627,7 +3627,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67dfaf9e49894cb6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68f46440827e4a03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3647,7 +3647,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="2" t="str">
-        <x:v>后端接口与阶段</x:v>
+        <x:v>Backend API and Phase</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -3658,7 +3658,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>这里是拟议的平台接口；第三方能力需核对当前官方文档和账户权限。</x:v>
+        <x:v>This is the proposed platform API; third-party capabilities need to be verified against the current official documentation and account permissions</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -3678,25 +3678,25 @@
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="8" t="str">
-        <x:v>接口ID</x:v>
+        <x:v>API ID</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
-        <x:v>接口或契约</x:v>
+        <x:v>API or Contract</x:v>
       </x:c>
       <x:c r="C4" s="8" t="str">
-        <x:v>期次</x:v>
+        <x:v>Phase</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
-        <x:v>输入</x:v>
+        <x:v>Input</x:v>
       </x:c>
       <x:c r="E4" s="8" t="str">
-        <x:v>输出</x:v>
+        <x:v>Output</x:v>
       </x:c>
       <x:c r="F4" s="8" t="str">
-        <x:v>关键约束</x:v>
+        <x:v>Key Constraints</x:v>
       </x:c>
       <x:c r="G4" s="8" t="str">
-        <x:v>需求ID</x:v>
+        <x:v>Requirement ID</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
@@ -3716,7 +3716,7 @@
         <x:v>document_id + status</x:v>
       </x:c>
       <x:c r="F5" s="5" t="str">
-        <x:v>422 类型/大小；私有存储</x:v>
+        <x:v>422 type/size; private storage</x:v>
       </x:c>
       <x:c r="G5" s="5" t="str">
         <x:v>P1-06</x:v>
@@ -3739,7 +3739,7 @@
         <x:v>parsed_fields + evidence_spans</x:v>
       </x:c>
       <x:c r="F6" s="9" t="str">
-        <x:v>解析任务可轮询；扫描件明确拒绝</x:v>
+        <x:v>Task parsing can poll; scanned documents clearly reject</x:v>
       </x:c>
       <x:c r="G6" s="9" t="str">
         <x:v>P1-07</x:v>
@@ -3756,13 +3756,13 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>用户确认字段+source_refs</x:v>
+        <x:v>User confirmed fields + source_refs</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
         <x:v>persona_version_id</x:v>
       </x:c>
       <x:c r="F7" s="5" t="str">
-        <x:v>不可变版本；校验归属</x:v>
+        <x:v>Immutable version; validate ownership</x:v>
       </x:c>
       <x:c r="G7" s="5" t="str">
         <x:v>P1-07</x:v>
@@ -3785,7 +3785,7 @@
         <x:v>people + next_cursor + capabilities</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
-        <x:v>不承诺全部高级过滤；429明确</x:v>
+        <x:v>No promise of all advanced filtering; 429 clearly defined</x:v>
       </x:c>
       <x:c r="G8" s="9" t="str">
         <x:v>P1-09</x:v>
@@ -3808,7 +3808,7 @@
         <x:v>records + per_item_status</x:v>
       </x:c>
       <x:c r="F9" s="5" t="str">
-        <x:v>按需有限批量；无邮箱为unknown</x:v>
+        <x:v>On-demand limited batch; no email is unknown</x:v>
       </x:c>
       <x:c r="G9" s="5" t="str">
         <x:v>P1-10</x:v>
@@ -3831,7 +3831,7 @@
         <x:v>generation_id + candidate + warnings</x:v>
       </x:c>
       <x:c r="F10" s="9" t="str">
-        <x:v>无工具执行权限；保留输入版本</x:v>
+        <x:v>No tool execution permissions; retain input version</x:v>
       </x:c>
       <x:c r="G10" s="9" t="str">
         <x:v>P1-18</x:v>
@@ -3854,7 +3854,7 @@
         <x:v>draft + new_revision</x:v>
       </x:c>
       <x:c r="F11" s="5" t="str">
-        <x:v>409返回冲突，不静默覆盖</x:v>
+        <x:v>409 return conflict, do not silently overwrite</x:v>
       </x:c>
       <x:c r="G11" s="5" t="str">
         <x:v>P1-23</x:v>
@@ -3877,7 +3877,7 @@
         <x:v>rendered + missing_variables</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
-        <x:v>统一确定性变量渲染</x:v>
+        <x:v>Uniform deterministic variable rendering</x:v>
       </x:c>
       <x:c r="G12" s="9" t="str">
         <x:v>P1-22</x:v>
@@ -3900,7 +3900,7 @@
         <x:v>authorization redirect</x:v>
       </x:c>
       <x:c r="F13" s="5" t="str">
-        <x:v>回调独立于平台登录</x:v>
+        <x:v>Callback independent of platform login</x:v>
       </x:c>
       <x:c r="G13" s="5" t="str">
         <x:v>P2-02</x:v>
@@ -3923,7 +3923,7 @@
         <x:v>job_id + state</x:v>
       </x:c>
       <x:c r="F14" s="9" t="str">
-        <x:v>Idempotency-Key；unknown先核对</x:v>
+        <x:v>Idempotency-Key; unknowns first verify</x:v>
       </x:c>
       <x:c r="G14" s="9" t="str">
         <x:v>P2-08</x:v>
@@ -3946,7 +3946,7 @@
         <x:v>sync_run + latest cursor</x:v>
       </x:c>
       <x:c r="F15" s="5" t="str">
-        <x:v>游标失效恢复；不可跨租户</x:v>
+        <x:v>Cursor expiration recovery; not cross-tenant</x:v>
       </x:c>
       <x:c r="G15" s="5" t="str">
         <x:v>P3-01</x:v>
@@ -3969,7 +3969,7 @@
         <x:v>send_job</x:v>
       </x:c>
       <x:c r="F16" s="9" t="str">
-        <x:v>保留会话头；按二期发送</x:v>
+        <x:v>Retain session header; send as phase two</x:v>
       </x:c>
       <x:c r="G16" s="9" t="str">
         <x:v>P3-04</x:v>
@@ -3992,7 +3992,7 @@
         <x:v>task</x:v>
       </x:c>
       <x:c r="F17" s="5" t="str">
-        <x:v>只提醒不发送</x:v>
+        <x:v>Only remind, do not send</x:v>
       </x:c>
       <x:c r="G17" s="5" t="str">
         <x:v>P3-08</x:v>
@@ -4015,7 +4015,7 @@
         <x:v>campaign + jobs</x:v>
       </x:c>
       <x:c r="F18" s="9" t="str">
-        <x:v>审阅过期拒绝；逐人任务</x:v>
+        <x:v>Review expiration rejection; individual task</x:v>
       </x:c>
       <x:c r="G18" s="9" t="str">
         <x:v>P4-03</x:v>
@@ -4038,7 +4038,7 @@
         <x:v>result/source/capability/error</x:v>
       </x:c>
       <x:c r="F19" s="5" t="str">
-        <x:v>骨架返回明确未实现</x:v>
+        <x:v>Skeleton returns clearly unimplemented</x:v>
       </x:c>
       <x:c r="G19" s="5" t="str">
         <x:v>P4-07</x:v>
@@ -4047,7 +4047,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50ad987555c24992"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0c3fc1e9f3540a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4066,7 +4066,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="2" t="str">
-        <x:v>关键验收场景</x:v>
+        <x:v>Key Acceptance Scenarios</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -4076,7 +4076,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>本表是待执行测试；不代表已完成真实API验证。</x:v>
+        <x:v>This table represents pending tests; does not represent completed real API verification</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -4094,22 +4094,22 @@
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="8" t="str">
-        <x:v>测试ID</x:v>
+        <x:v>Test ID</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
-        <x:v>期次</x:v>
+        <x:v>Phase</x:v>
       </x:c>
       <x:c r="C4" s="8" t="str">
-        <x:v>需求ID</x:v>
+        <x:v>Requirement ID</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
-        <x:v>场景</x:v>
+        <x:v>Scenario</x:v>
       </x:c>
       <x:c r="E4" s="8" t="str">
-        <x:v>预期结果</x:v>
+        <x:v>Expected result</x:v>
       </x:c>
       <x:c r="F4" s="8" t="str">
-        <x:v>建议验证证据</x:v>
+        <x:v>Recommended Verification Evidence</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
@@ -4120,16 +4120,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>P1-06、P1-07</x:v>
+        <x:v>P1-06, P1-07</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>上传文本简历并修改学校</x:v>
+        <x:v>Upload text resume and modify school</x:v>
       </x:c>
       <x:c r="E5" s="5" t="str">
-        <x:v>来源片段保留；确认后生成新画像版本</x:v>
+        <x:v>Source fragment retained; generate new persona version after confirmation</x:v>
       </x:c>
       <x:c r="F5" s="5" t="str">
-        <x:v>文件+界面+DB版本</x:v>
+        <x:v>File + interface + DB version</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="64" customHeight="1">
@@ -4140,16 +4140,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>P1-08、P1-09</x:v>
+        <x:v>P1-08, P1-09</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>无画像直接搜索并手动写信</x:v>
+        <x:v>Search without persona and manually write email</x:v>
       </x:c>
       <x:c r="E6" s="9" t="str">
-        <x:v>模块不被强制向导阻挡</x:v>
+        <x:v>Modules not blocked by forced wizard</x:v>
       </x:c>
       <x:c r="F6" s="9" t="str">
-        <x:v>UI操作录像或截图</x:v>
+        <x:v>UI operation recording or screenshot</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="64" customHeight="1">
@@ -4163,13 +4163,13 @@
         <x:v>P1-13</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>Apollo 与 LinkedIn 线索对应同一人、同名异人及职位冲突</x:v>
+        <x:v>Apollo and LinkedIn leads correspond to same person, same name different person, and position conflict</x:v>
       </x:c>
       <x:c r="E7" s="5" t="str">
-        <x:v>同人核对后关联来源；同名不误合并；冲突保留，摘要不自动升级为事实</x:v>
+        <x:v>After same person verification, associate source; same name not mistakenly merged; conflicts retained, summary not automatically upgraded to fact</x:v>
       </x:c>
       <x:c r="F7" s="5" t="str">
-        <x:v>联系人、来源关联、冲突记录及真实检索证据</x:v>
+        <x:v>Contact, source association, conflict record, and real retrieval evidence</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="64" customHeight="1">
@@ -4180,16 +4180,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>P1-17、P1-18</x:v>
+        <x:v>P1-17, P1-18</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>联系人学校未知，要求校友开头</x:v>
+        <x:v>Contact school unknown, require alumni prefix</x:v>
       </x:c>
       <x:c r="E8" s="9" t="str">
-        <x:v>提示无依据；不生成共同学校陈述</x:v>
+        <x:v>Warn that there is no supporting evidence; do not generate common school statement</x:v>
       </x:c>
       <x:c r="F8" s="9" t="str">
-        <x:v>生成输入/输出脱敏记录</x:v>
+        <x:v>Redacted generation input/output records</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="64" customHeight="1">
@@ -4200,16 +4200,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>P1-18、P1-19</x:v>
+        <x:v>P1-18, P1-19</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>已有手写正文后触发生成</x:v>
+        <x:v>Trigger generation after existing manually written body</x:v>
       </x:c>
       <x:c r="E9" s="5" t="str">
-        <x:v>正文不变，候选在建议区；丢弃无损</x:v>
+        <x:v>Body unchanged, candidates in suggestion area; discard without loss</x:v>
       </x:c>
       <x:c r="F9" s="5" t="str">
-        <x:v>编辑前后版本</x:v>
+        <x:v>Before and after edit versions</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="64" customHeight="1">
@@ -4220,16 +4220,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
-        <x:v>P1-20、P1-23</x:v>
+        <x:v>P1-20, P1-23</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>生成中修改正文再接收结果</x:v>
+        <x:v>Generate and modify body again to receive results</x:v>
       </x:c>
       <x:c r="E10" s="9" t="str">
-        <x:v>候选标过期；应用被阻止</x:v>
+        <x:v>Candidate marked expired; application blocked</x:v>
       </x:c>
       <x:c r="F10" s="9" t="str">
-        <x:v>revision与响应记录</x:v>
+        <x:v>revision and response record</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="64" customHeight="1">
@@ -4243,13 +4243,13 @@
         <x:v>P1-22</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
-        <x:v>姓名缺失或未知变量</x:v>
+        <x:v>Missing name or unknown variable</x:v>
       </x:c>
       <x:c r="E11" s="5" t="str">
-        <x:v>定位缺失并阻止 Ready；补齐可预览</x:v>
+        <x:v>Locate missing and block Ready; fill in to preview</x:v>
       </x:c>
       <x:c r="F11" s="5" t="str">
-        <x:v>预览和验证清单</x:v>
+        <x:v>Preview and verification checklist</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="64" customHeight="1">
@@ -4263,13 +4263,13 @@
         <x:v>P1-23</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>断网保存失败及双标签页冲突</x:v>
+        <x:v>Save failure on disconnection and dual tab conflict</x:v>
       </x:c>
       <x:c r="E12" s="9" t="str">
-        <x:v>不假 Saved；409保留双方；恢复可保存</x:v>
+        <x:v>No fake Saved; 409 retain both; recovery can save</x:v>
       </x:c>
       <x:c r="F12" s="9" t="str">
-        <x:v>模拟错误及恢复记录</x:v>
+        <x:v>Simulated error and recovery record</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="64" customHeight="1">
@@ -4283,13 +4283,13 @@
         <x:v>P1-26</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
-        <x:v>真实API返回429或403</x:v>
+        <x:v>Real API returns 429 or 403</x:v>
       </x:c>
       <x:c r="E13" s="5" t="str">
-        <x:v>显示错误，不回退模拟数据</x:v>
+        <x:v>Display error, do not rollback simulated data</x:v>
       </x:c>
       <x:c r="F13" s="5" t="str">
-        <x:v>Provider错误记录</x:v>
+        <x:v>Provider error record</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="64" customHeight="1">
@@ -4303,13 +4303,13 @@
         <x:v>P2-01</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>用户A访问B草稿/文件/邮箱ID</x:v>
+        <x:v>User A accesses B draft/file/email ID</x:v>
       </x:c>
       <x:c r="E14" s="9" t="str">
-        <x:v>请求被拒；对象存在性不泄露</x:v>
+        <x:v>Request rejected; object existence not leaked</x:v>
       </x:c>
       <x:c r="F14" s="9" t="str">
-        <x:v>跨租户接口测试</x:v>
+        <x:v>Cross-tenant interface test</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="64" customHeight="1">
@@ -4320,16 +4320,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C15" s="5" t="str">
-        <x:v>P2-02、P2-06</x:v>
+        <x:v>P2-02, P2-06</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
-        <x:v>登录后连接不同 Gmail 并测试发送</x:v>
+        <x:v>Login and connect different Gmail mailboxes and test sending</x:v>
       </x:c>
       <x:c r="E15" s="5" t="str">
-        <x:v>用户指定地址收到邮件；测试不计正式统计</x:v>
+        <x:v>User-specified address receives email; test not counted in formal statistics</x:v>
       </x:c>
       <x:c r="F15" s="5" t="str">
-        <x:v>脱敏provider ID和收件记录</x:v>
+        <x:v>Anonymize provider ID and recipient record</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="64" customHeight="1">
@@ -4340,16 +4340,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C16" s="9" t="str">
-        <x:v>P2-08、P2-09</x:v>
+        <x:v>P2-08, P2-09</x:v>
       </x:c>
       <x:c r="D16" s="9" t="str">
-        <x:v>重复点击、Worker重启、响应超时</x:v>
+        <x:v>Repeated clicks, Worker restart, response timeout</x:v>
       </x:c>
       <x:c r="E16" s="9" t="str">
-        <x:v>任务不重复；unknown不盲目重发</x:v>
+        <x:v>Task not repeated; unknowns not blindly resent</x:v>
       </x:c>
       <x:c r="F16" s="9" t="str">
-        <x:v>任务表和SendAttempt</x:v>
+        <x:v>Task table and SendAttempt</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="64" customHeight="1">
@@ -4363,13 +4363,13 @@
         <x:v>P2-08</x:v>
       </x:c>
       <x:c r="D17" s="5" t="str">
-        <x:v>非工作时段、DST边界及取消任务</x:v>
+        <x:v>Non-working hours, DST boundary, and canceled tasks</x:v>
       </x:c>
       <x:c r="E17" s="5" t="str">
-        <x:v>按配置窗口执行；取消前未提交</x:v>
+        <x:v>Execute according to configuration window; not submitted before cancellation</x:v>
       </x:c>
       <x:c r="F17" s="5" t="str">
-        <x:v>时间计算测试</x:v>
+        <x:v>Time calculation test</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="64" customHeight="1">
@@ -4380,16 +4380,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C18" s="9" t="str">
-        <x:v>P3-01、P3-02</x:v>
+        <x:v>P3-01, P3-02</x:v>
       </x:c>
       <x:c r="D18" s="9" t="str">
-        <x:v>重复增量事件、乱序事件、游标过期</x:v>
+        <x:v>Repeated incremental events, out-of-order events, cursor expiration</x:v>
       </x:c>
       <x:c r="E18" s="9" t="str">
-        <x:v>去重且可恢复，旧会话仍关联</x:v>
+        <x:v>Deduplicate and recoverable, old session still associated</x:v>
       </x:c>
       <x:c r="F18" s="9" t="str">
-        <x:v>同步游标与消息唯一键</x:v>
+        <x:v>Synchronize cursor with message unique key</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="64" customHeight="1">
@@ -4403,13 +4403,13 @@
         <x:v>P3-04</x:v>
       </x:c>
       <x:c r="D19" s="5" t="str">
-        <x:v>从指定收件邮箱回复再从平台回信</x:v>
+        <x:v>Reply from specified recipient email and then reply from platform</x:v>
       </x:c>
       <x:c r="E19" s="5" t="str">
-        <x:v>双方同一目标会话可查看</x:v>
+        <x:v>Both parties can view the same target session</x:v>
       </x:c>
       <x:c r="F19" s="5" t="str">
-        <x:v>消息头及实际会话截图</x:v>
+        <x:v>Message header and actual session screenshot</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="64" customHeight="1">
@@ -4423,13 +4423,13 @@
         <x:v>P3-06</x:v>
       </x:c>
       <x:c r="D20" s="9" t="str">
-        <x:v>已有定时邮件时收到回复</x:v>
+        <x:v>Receive reply when there is already a scheduled email</x:v>
       </x:c>
       <x:c r="E20" s="9" t="str">
-        <x:v>待发暂停；人工明确后才恢复</x:v>
+        <x:v>Paused for sending; resume only after manual confirmation</x:v>
       </x:c>
       <x:c r="F20" s="9" t="str">
-        <x:v>SendJob状态与原因</x:v>
+        <x:v>SendJob status and reason</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="64" customHeight="1">
@@ -4440,16 +4440,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C21" s="5" t="str">
-        <x:v>P3-08、P3-09</x:v>
+        <x:v>P3-08, P3-09</x:v>
       </x:c>
       <x:c r="D21" s="5" t="str">
-        <x:v>跟进任务到期</x:v>
+        <x:v>Follow-up task expiration</x:v>
       </x:c>
       <x:c r="E21" s="5" t="str">
-        <x:v>只提醒，外部发送数不变</x:v>
+        <x:v>Only remind, external sent count unchanged</x:v>
       </x:c>
       <x:c r="F21" s="5" t="str">
-        <x:v>任务与发件记录对比</x:v>
+        <x:v>Task vs. sender record comparison</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="64" customHeight="1">
@@ -4463,13 +4463,13 @@
         <x:v>P3-07</x:v>
       </x:c>
       <x:c r="D22" s="9" t="str">
-        <x:v>退订后切换另一个已连接邮箱发信</x:v>
+        <x:v>Switch to another connected email after unsubscribing</x:v>
       </x:c>
       <x:c r="E22" s="9" t="str">
-        <x:v>工作区级屏蔽仍生效</x:v>
+        <x:v>Workspace-level suppression still effective</x:v>
       </x:c>
       <x:c r="F22" s="9" t="str">
-        <x:v>suppression和预检记录</x:v>
+        <x:v>suppression and pre-check record</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="64" customHeight="1">
@@ -4480,16 +4480,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C23" s="5" t="str">
-        <x:v>P4-02、P4-03</x:v>
+        <x:v>P4-02, P4-03</x:v>
       </x:c>
       <x:c r="D23" s="5" t="str">
-        <x:v>十人名单含重复/缺变量/被屏蔽者</x:v>
+        <x:v>Ten-person list contains duplicates/missing variables/blocked contacts</x:v>
       </x:c>
       <x:c r="E23" s="5" t="str">
-        <x:v>异常汇总，明确排除后逐人发送</x:v>
+        <x:v>Anomaly summary, explicitly exclude after confirmation, then send individually</x:v>
       </x:c>
       <x:c r="F23" s="5" t="str">
-        <x:v>预览与快照逐条比较</x:v>
+        <x:v>Preview and snapshot comparison per item</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="64" customHeight="1">
@@ -4503,13 +4503,13 @@
         <x:v>P4-04</x:v>
       </x:c>
       <x:c r="D24" s="9" t="str">
-        <x:v>活动暂停后恢复并单人退出</x:v>
+        <x:v>Campaign paused, resume and individual exit</x:v>
       </x:c>
       <x:c r="E24" s="9" t="str">
-        <x:v>窗口重算，退出人不发送</x:v>
+        <x:v>Recalculate window, excluded contacts not sent</x:v>
       </x:c>
       <x:c r="F24" s="9" t="str">
-        <x:v>队列与活动记录</x:v>
+        <x:v>Queue and campaign record</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="64" customHeight="1">
@@ -4523,13 +4523,13 @@
         <x:v>P4-05</x:v>
       </x:c>
       <x:c r="D25" s="5" t="str">
-        <x:v>测试、自动回复、正式发送混合样本</x:v>
+        <x:v>Test, auto-reply, and formal send mixed samples</x:v>
       </x:c>
       <x:c r="E25" s="5" t="str">
-        <x:v>正式人数去重；人工回复独立；分母一致</x:v>
+        <x:v>Formal deduplicated count; manual replies independent; denominator consistent</x:v>
       </x:c>
       <x:c r="F25" s="5" t="str">
-        <x:v>事件明细和统计查询</x:v>
+        <x:v>Event details and statistics query</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="64" customHeight="1">
@@ -4543,19 +4543,19 @@
         <x:v>P4-07</x:v>
       </x:c>
       <x:c r="D26" s="9" t="str">
-        <x:v>调用未实现导师provider</x:v>
+        <x:v>Call unimplemented mentor provider</x:v>
       </x:c>
       <x:c r="E26" s="9" t="str">
-        <x:v>明确Unavailable，无伪造导师</x:v>
+        <x:v>Clearly Unavailable, no fabricated mentors</x:v>
       </x:c>
       <x:c r="F26" s="9" t="str">
-        <x:v>契约测试结果</x:v>
+        <x:v>Contract test results</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f4c63c4ff434e54"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R424f8a64fc7b456c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4572,7 +4572,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="2" t="str">
-        <x:v>四期完整开发 Prompt</x:v>
+        <x:v>Four-Phase Complete Development Prompt</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -4580,7 +4580,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>筛选期次后，按段落序号复制正文；可直接使用同目录的独立 Markdown 文件。</x:v>
+        <x:v>After filtering by phase, copy the body by paragraph number; can be directly used with the independent Markdown files in the same directory</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -4594,19 +4594,19 @@
     </x:row>
     <x:row r="4" ht="32" customHeight="1">
       <x:c r="A4" s="8" t="str">
-        <x:v>期次</x:v>
+        <x:v>Phase</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
-        <x:v>文件</x:v>
+        <x:v>File</x:v>
       </x:c>
       <x:c r="C4" s="8" t="str">
-        <x:v>段落</x:v>
+        <x:v>Paragraph</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
-        <x:v>Prompt正文</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="44" customHeight="1">
+        <x:v>Prompt Body</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="52" customHeight="1">
       <x:c r="A5" s="5" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -4617,10 +4617,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str">
-        <x:v>请开发 Connact.ai 第 1 期：简历找人与 AI 写作。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="120" customHeight="1">
+        <x:v>Please develop Connact.ai Phase 1: Resume-based People Search and AI Writing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="137" customHeight="1">
       <x:c r="A6" s="9" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -4631,12 +4631,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D6" s="19" t="str">
-        <x:v>已确认约束：个人工作区可连接多个 Gmail，团队仅预留；默认英文界面并支持简体中文，邮件语言独立；Finance 是核心，Academic 仅占位与契约；四期均不做自动序列。所有模块独立可用，不强制分步向导。不要把 Mock 或 HTML 演示当作真实集成。
-管理员后端已列为 Soon 待排期，不属于 P1–P4 的实现范围；只保留 Coming Soon 入口与范围说明，不开放真实管理操作。平台管理员与个人工作区 Owner 是不同角色。
-先检查工作区、AGENTS.md 和已实现代码，给出简短实施顺序后直接开发。延续已有数据和模块，不重建整个项目。第三方能力查当前官方文档；没有凭据可显式 Mock，真实失败不能偷偷回退模拟。交付代码、迁移、启动说明、关键验证及真实未验证项。涉及真实发信仅用用户指定测试收件人。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="52" customHeight="1">
+        <x:v>Confirmed Constraints: Personal workspaces can connect to multiple Gmail mailboxes, teams are reserved; default English interface with support for Simplified Chinese, email language is independent; Finance is core, Academic is placeholder and contract; no automated email sequences in any phase. All modules are independent and usable, no forced step-by-step wizard. Do not treat Mock or HTML demos as real integrations.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="86" customHeight="1">
       <x:c r="A7" s="5" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -4647,10 +4645,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D7" s="18" t="str">
-        <x:v>本次只开发第一期最小 MVP：上传简历/手动画像 → 搜索金融联系人 → 看推荐理由 → 保存联系人 → AI 写信 → 编辑、变量预览和保存/复制草稿。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="69" customHeight="1">
+        <x:v>Admin backend is listed as Soon, not part of P1–P4 implementation; only retain Coming Soon entry and scope description, no real management operations. Platform admin and personal workspace owner are different roles.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="154" customHeight="1">
       <x:c r="A8" s="9" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -4661,10 +4659,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="D8" s="19" t="str">
-        <x:v>布局：专业 B2B 工作台，左导航、顶部上下文、主内容区及联系人抽屉。Dashboard、Finance、Personas、People Search、Contacts、Email Studio 可用。Academic、Templates、Mailboxes、Inbox、Campaigns、Analytics 为明确 Coming Soon。画像不是搜索或手写草稿的强制前置。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="52" customHeight="1">
+        <x:v>First check workspace, AGENTS.md, and implemented code, provide a short implementation order, then proceed with development. Continue with existing data and modules, do not rebuild the entire project. Third-party capabilities check current official documentation; without credentials, explicitly Mock, real failures cannot be silently rolled back. Deliver code, migration, startup instructions, key validations, and real unverified items. Real sending only uses user-specified test recipients.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="86" customHeight="1">
       <x:c r="A9" s="5" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -4675,7 +4673,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="D9" s="18" t="str">
-        <x:v>画像：文本型 PDF/DOCX，10 MB 上限，私有存储；提取教育/工作/技能/金融领域/地区/职业目标。保留原文证据，用户校对确认后建立版本。扫描件未支持时说明限制；支持手填及多个画像。</x:v>
+        <x:v>This phase only develops the minimal MVP: upload resume/draw persona → search financial contacts → view recommendation rationale → save contact → AI write email → edit, variable preview, and save/copy draft.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="120" customHeight="1">
@@ -4689,10 +4687,10 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="D10" s="19" t="str">
-        <x:v>搜索：后端 Apollo 提供结构化人员搜索与按需 enrichment；SerpAPI 通过 Google 定向检索 LinkedIn 公开档案（如 site:linkedin.com/in/ 加姓名与机构），不直接调用 LinkedIn API。两者围绕同一 Contact 相互补充：Apollo 信息定位 LinkedIn，核对后的 LinkedIn URL/职业信息反向辅助 Apollo 匹配；现有适配器只有通用搜索与 Apollo ID 补充，定向查询及反向匹配需实现后验证。独立保留来源与获取时间，摘要保持待核实，冲突不覆盖，不按同名自动合并。实现职位/机构/地区/关键词分页、来源和时间、有限批量补充。邮箱未知如实显示。基于选定画像及来源生成简短推荐理由，不编造校友关系。保存按提供商 ID 去重，支持手工联系人、标签和备注。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="86" customHeight="1">
+        <x:v>Layout: Professional B2B workspace, left navigation, top context, main content area, and contact drawer. Dashboard, Finance, Personas, People Search, Contacts, Email Studio are available. Academic, Templates, Mailboxes, Inbox, Campaigns, Analytics are explicitly Coming Soon. Persona is not a mandatory prerequisite for search or hand-written draft.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="103" customHeight="1">
       <x:c r="A11" s="5" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -4703,10 +4701,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D11" s="18" t="str">
-        <x:v>AI 写作：在联系人和画像基础上设置目的、CTA、语言、语气、长度。右侧显示可用证据与缺口，允许选取用于写信的事实。生成结构化 subject/body/claims/warnings，在建议区展示，不覆盖正文。支持比较、采纳、丢弃、撤销与局部缩短/改写；建议绑定草稿 revision，过期结果不覆盖新稿。使用 Tiptap 基础富文本与变量节点，缺失变量明确定位；复制内容必须与预览一致。服务端防抖保存、版本冲突保留双方内容；提供草稿库及三个 Finance 写作起点。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="86" customHeight="1">
+        <x:v>Persona: Text-based PDF/DOCX, 10 MB limit, private storage; extract education/work/skills/financial domain/region/career goals. Retain original evidence, user review and confirmation to establish version. When scanned documents are not supported, explain the limitation; support hand-filled and multiple personas.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="307" customHeight="1">
       <x:c r="A12" s="9" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -4717,10 +4715,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D12" s="19" t="str">
-        <x:v>技术：Next.js/React/TypeScript/Tiptap + FastAPI + PostgreSQL + Docker Compose。固定本地 workspace，所有查询限定 workspace_id；该模式只限本地。封装搜索、补充、公开搜索、AI Provider。保存 PersonaVersion、SourceEvidence、MatchAssessment、GenerationRun、DraftRevision。第一期不装 Redis、不开发登录、邮箱或发送。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="52" customHeight="1">
+        <x:v>Search: Backend Apollo provides structured people search and on-demand enrichment; SerpAPI performs targeted LinkedIn public profile search via Google (e.g., site:linkedin.com/in/ with name and organization), does not directly call LinkedIn API. Both work around the same Contact to complement each other: Apollo information locates LinkedIn, verified LinkedIn URL/career information assists Apollo matching; existing adapters only have general search and Apollo ID supplement, targeted queries and reverse matching need to be implemented and validated. Keep sources and acquisition time separately, summary remains unverified, conflicts not overwritten, no automatic merging by same name. Implement job/organization/region/keyword pagination, source and time, limited batch supplementation. Unknown email is displayed as-is. Generate short recommendation rationale based on selected persona and source, do not fabricate alumni relationships. Save by provider ID to avoid duplicates, support manual contacts, tags, and notes.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="205" customHeight="1">
       <x:c r="A13" s="5" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -4731,37 +4729,35 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="D13" s="18" t="str">
-        <x:v>验收：刷新后画像/联系人/草稿存在；同人不重复保存；无证据不造事实；生成失败保留原稿；变量缺失不能标 Ready；旧建议不能覆盖新编辑；Mock 明示；英文默认及中文切换可用。交付可运行闭环，不停在页面骨架。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="44" customHeight="1">
+        <x:v>AI Writing: Set purpose, CTA, language, tone, and length based on contact and persona. Display available evidence and gaps on the right, allow selection of facts for writing. Generate structured subject/body/claims/warnings, display in suggestion area, do not overwrite the main text. Support comparison, adoption, discard, undo, and partial shortening/rewriting; suggestions should be bound to draft revision, expired results do not overwrite new drafts. Use Tiptap base rich text and variable nodes, missing variables are clearly identified; copied content must match preview. Server-side debounce save, version conflicts retain both contents; provide draft library and three Finance writing starters.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="137" customHeight="1">
       <x:c r="A14" s="9" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>prompt-02-mailboxes-send.md</x:v>
+        <x:v>prompt-01-mvp.md</x:v>
       </x:c>
       <x:c r="C14" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D14" s="19" t="str">
-        <x:v>请开发 Connact.ai 第 2 期：账户 Gmail 与单封发送。</x:v>
+        <x:v>Technology: Next.js/React/TypeScript/Tiptap + FastAPI + PostgreSQL + Docker Compose. Fixed local workspace, all queries limited to workspace_id; this mode is only for local use. Encapsulate search, enrichment, public search, and AI Provider. Save PersonaVersion, SourceEvidence, MatchAssessment, GenerationRun, DraftRevision. Phase 1 does not install Redis, does not develop login, email, or sending.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="120" customHeight="1">
       <x:c r="A15" s="5" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>prompt-02-mailboxes-send.md</x:v>
+        <x:v>prompt-01-mvp.md</x:v>
       </x:c>
       <x:c r="C15" s="5" t="n">
-        <x:v>2</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D15" s="18" t="str">
-        <x:v>已确认约束：个人工作区可连接多个 Gmail，团队仅预留；默认英文界面并支持简体中文，邮件语言独立；Finance 是核心，Academic 仅占位与契约；四期均不做自动序列。所有模块独立可用，不强制分步向导。不要把 Mock 或 HTML 演示当作真实集成。
-管理员后端已列为 Soon 待排期，不属于 P1–P4 的实现范围；只保留 Coming Soon 入口与范围说明，不开放真实管理操作。平台管理员与个人工作区 Owner 是不同角色。
-先检查工作区、AGENTS.md 和已实现代码，给出简短实施顺序后直接开发。延续已有数据和模块，不重建整个项目。第三方能力查当前官方文档；没有凭据可显式 Mock，真实失败不能偷偷回退模拟。交付代码、迁移、启动说明、关键验证及真实未验证项。涉及真实发信仅用用户指定测试收件人。</x:v>
+        <x:v>Acceptance: After refresh, personas/contacts/drafts exist; same person not duplicated; no facts created without evidence; generation failure retains original draft; missing variables cannot mark Ready; old suggestions cannot overwrite new edits; Mocks are explicitly stated; English default and Chinese switch are available. Deliver a runnable loop, not just page skeleton.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="52" customHeight="1">
@@ -4772,13 +4768,13 @@
         <x:v>prompt-02-mailboxes-send.md</x:v>
       </x:c>
       <x:c r="C16" s="9" t="n">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="19" t="str">
-        <x:v>在第一期代码上开发第二期：正式账户、多个 Gmail、单封测试/正式/定时发送。不要开发完整 Inbox、批量 Campaign 或自动跟进。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="52" customHeight="1">
+        <x:v>Please develop Connact.ai Phase 2: Account Gmail and Single-Send.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="137" customHeight="1">
       <x:c r="A17" s="5" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -4786,13 +4782,13 @@
         <x:v>prompt-02-mailboxes-send.md</x:v>
       </x:c>
       <x:c r="C17" s="5" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D17" s="18" t="str">
-        <x:v>账户：实现 Google 平台登录及 User/Workspace/Membership，个人工作区一个 Owner。现有本地演示数据显式迁移/认领，不能自动归给任意登录用户。两个测试用户必须完成 API/文件/数据隔离验证；生产配置禁用演示登录。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="69" customHeight="1">
+        <x:v>Confirmed Constraints: Personal workspaces can connect to multiple Gmail mailboxes, teams are reserved; default English interface with support for Simplified Chinese, email language is independent; Finance is core, Academic is placeholder and contract; no automated email sequences in any phase. All modules are independent and usable, no forced step-by-step wizard. Do not treat Mock or HTML demos as real integrations.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="86" customHeight="1">
       <x:c r="A18" s="9" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -4800,13 +4796,13 @@
         <x:v>prompt-02-mailboxes-send.md</x:v>
       </x:c>
       <x:c r="C18" s="9" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D18" s="19" t="str">
-        <x:v>邮箱：Google 平台登录与 Gmail 授权分开，一个用户可连接多个且与登录地址不同。OAuth state、安全回调、适用 PKCE；Token/Refresh Token 服务端加密，密钥与数据库分开。支持刷新、失效、断连/重授权、授权发件身份、平台签名、时区、合法发送窗口和平台限额。按功能申请必要权限，公开上线审核单独说明。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="52" customHeight="1">
+        <x:v>Admin backend is listed as Soon, not part of P1–P4 implementation; only retain Coming Soon entry and scope description, no real management operations. Platform admin and personal workspace owner are different roles.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="154" customHeight="1">
       <x:c r="A19" s="5" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -4814,10 +4810,10 @@
         <x:v>prompt-02-mailboxes-send.md</x:v>
       </x:c>
       <x:c r="C19" s="5" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D19" s="18" t="str">
-        <x:v>发送：复用一期草稿和预览，发送前检查收件地址、变量、附件、HTML、屏蔽列表及邮箱状态，冻结用户确认的内容版本。测试默认发给自己的指定邮箱，不能计入正式触达。正式单封由用户明确确认；sent 只表示提供商接受。附件必须用户主动选择，检查编码后总大小。</x:v>
+        <x:v>First check workspace, AGENTS.md, and implemented code, provide a short implementation order, then proceed with development. Continue with existing data and modules, do not rebuild the entire project. Third-party capabilities check current official documentation; without credentials, explicitly Mock, real failures cannot be silently rolled back. Deliver code, migration, startup instructions, key validations, and real unverified items. Real sending only uses user-specified test recipients.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="69" customHeight="1">
@@ -4828,13 +4824,13 @@
         <x:v>prompt-02-mailboxes-send.md</x:v>
       </x:c>
       <x:c r="C20" s="9" t="n">
-        <x:v>7</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D20" s="19" t="str">
-        <x:v>定时：加入 Redis/Worker，PostgreSQL 持久化 SendJob/SendAttempt，按邮箱时区和窗口执行。支持取消、暂停、重启恢复。API 幂等键、任务唯一约束与执行锁配合防重。可能已发送但响应超时标 unknown，先核对，不盲目重试。断连/失效停止该邮箱任务，手动禁止地址在工作区跨邮箱生效。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="52" customHeight="1">
+        <x:v>Develop Phase 2 on top of Phase 1 code: formal account, multiple Gmail mailboxes, single test/formal/scheduled send. Do not develop full Inbox, batch Campaign, or auto follow-up.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="120" customHeight="1">
       <x:c r="A21" s="5" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -4842,13 +4838,13 @@
         <x:v>prompt-02-mailboxes-send.md</x:v>
       </x:c>
       <x:c r="C21" s="5" t="n">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D21" s="18" t="str">
-        <x:v>接口预留 MailProvider 的同步/回复能力但本期不建 Inbox UI。记录 provider message/thread ID，便于三期关联。不要假设 Gmail 支持业务幂等键或绝对 exactly-once。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="52" customHeight="1">
+        <x:v>Account: Implement Google platform login and User/Workspace/Membership, one Owner per personal workspace. Existing local demo data is explicitly migrated/claimed, cannot be automatically assigned to any logged-in user. Two test users must complete API/file/data isolation validation; production configuration disables demo login.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="154" customHeight="1">
       <x:c r="A22" s="9" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -4856,71 +4852,69 @@
         <x:v>prompt-02-mailboxes-send.md</x:v>
       </x:c>
       <x:c r="C22" s="9" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D22" s="19" t="str">
+        <x:v>Email: Google platform login and Gmail authorization are separate, one user can connect to multiple and the login address is different. OAuth state, secure callback, applicable PKCE; Token/Refresh Token server-side encrypted, keys and database separated. Support refresh, expiration, disconnection/reauthorization, sender identity, platform signature, timezone, valid sending window, and platform limits. Apply for necessary permissions by function, separate explanation for public launch.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="137" customHeight="1">
+      <x:c r="A23" s="5" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B23" s="5" t="str">
+        <x:v>prompt-02-mailboxes-send.md</x:v>
+      </x:c>
+      <x:c r="C23" s="5" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D23" s="18" t="str">
+        <x:v>Sending: Reuse Phase 1 draft and preview, check recipient address, variables, attachments, HTML, block list, and email status before sending, freeze user-confirmed content version. Test defaults to sending to user's specified email, cannot count as formal delivery. Formal single send requires user confirmation; 'sent' only indicates provider acceptance. Attachments must be user-selected, check encoding and total size.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="137" customHeight="1">
+      <x:c r="A24" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B24" s="9" t="str">
+        <x:v>prompt-02-mailboxes-send.md</x:v>
+      </x:c>
+      <x:c r="C24" s="9" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D22" s="19" t="str">
-        <x:v>验收：两个用户与两个 Gmail 边界正确；重复点击不重复任务；指定测试邮箱完成真实发信；定时/取消/断连/unknown 场景测试。缺少凭据时交付真实适配器和 Mock 测试，标记真实集成未验证。保持一期画像搜索写作回归通过。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="44" customHeight="1">
-      <x:c r="A23" s="5" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B23" s="5" t="str">
-        <x:v>prompt-03-inbox-followup.md</x:v>
-      </x:c>
-      <x:c r="C23" s="5" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D23" s="18" t="str">
-        <x:v>请开发 Connact.ai 第 3 期：收件箱与手动跟进。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="120" customHeight="1">
-      <x:c r="A24" s="9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B24" s="9" t="str">
-        <x:v>prompt-03-inbox-followup.md</x:v>
-      </x:c>
-      <x:c r="C24" s="9" t="n">
+      <x:c r="D24" s="19" t="str">
+        <x:v>Scheduling: Add Redis/Worker, PostgreSQL persist SendJob/SendAttempt, execute by email timezone and window. Support cancel, pause, resume. API idempotency key, task uniqueness constraint, and execution lock prevent duplication. If already sent but response timeout, mark as unknown, first verify, do not blindly retry. Disconnection/failure stops the email task, manually banned address in workspace across emails takes effect.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="86" customHeight="1">
+      <x:c r="A25" s="5" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D24" s="19" t="str">
-        <x:v>已确认约束：个人工作区可连接多个 Gmail，团队仅预留；默认英文界面并支持简体中文，邮件语言独立；Finance 是核心，Academic 仅占位与契约；四期均不做自动序列。所有模块独立可用，不强制分步向导。不要把 Mock 或 HTML 演示当作真实集成。
-管理员后端已列为 Soon 待排期，不属于 P1–P4 的实现范围；只保留 Coming Soon 入口与范围说明，不开放真实管理操作。平台管理员与个人工作区 Owner 是不同角色。
-先检查工作区、AGENTS.md 和已实现代码，给出简短实施顺序后直接开发。延续已有数据和模块，不重建整个项目。第三方能力查当前官方文档；没有凭据可显式 Mock，真实失败不能偷偷回退模拟。交付代码、迁移、启动说明、关键验证及真实未验证项。涉及真实发信仅用用户指定测试收件人。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="44" customHeight="1">
-      <x:c r="A25" s="5" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="B25" s="5" t="str">
-        <x:v>prompt-03-inbox-followup.md</x:v>
+        <x:v>prompt-02-mailboxes-send.md</x:v>
       </x:c>
       <x:c r="C25" s="5" t="n">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D25" s="18" t="str">
-        <x:v>在前两期代码上开发第三期：集中 Inbox、原会话回复、手动跟进和对既有排期的回复保护。不开发自动下一封。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="69" customHeight="1">
+        <x:v>Interface reserves MailProvider's synchronous/reply capability but does not build Inbox UI in this phase. Record provider message/thread ID for association in Phase 3. Do not assume Gmail supports business idempotency key or absolute exactly-once.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="120" customHeight="1">
       <x:c r="A26" s="9" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B26" s="9" t="str">
-        <x:v>prompt-03-inbox-followup.md</x:v>
+        <x:v>prompt-02-mailboxes-send.md</x:v>
       </x:c>
       <x:c r="C26" s="9" t="n">
-        <x:v>4</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D26" s="19" t="str">
-        <x:v>同步：先读取最近 30 天并分页，持久化 history 游标，增量轮询默认两分钟并可手动刷新。游标失效执行恢复同步；进行中的旧会话继续跟踪。以 workspace/mailbox/provider message/thread ID 关联并去重，平台外在 Gmail 收发的消息也能进入会话。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="69" customHeight="1">
+        <x:v>Acceptance: Two users and two Gmail mailboxes boundary correct; duplicate click does not duplicate task; specified test email completes real sending; test scheduling/cancel/disconnection/unknown scenarios. Deliver real adapter and Mock test when credentials are missing, mark real integration unverified. Keep Phase 1 persona search writing regression passing.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="44" customHeight="1">
       <x:c r="A27" s="5" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -4928,13 +4922,13 @@
         <x:v>prompt-03-inbox-followup.md</x:v>
       </x:c>
       <x:c r="C27" s="5" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D27" s="18" t="str">
-        <x:v>Inbox：三栏为筛选、会话列表、正文与回复编辑器/联系人侧栏。支持邮箱、领域、未读、待回复和意向筛选；未知领域不自动归 Finance。已读与归档同步 Gmail；备注、意向、提醒只在平台。邮件 HTML 清理、远程图默认不加载；附件显示元数据及可用入口。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="52" customHeight="1">
+        <x:v>Please develop Connact.ai Phase 3: Inbox and Manual Follow-Up.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="137" customHeight="1">
       <x:c r="A28" s="9" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -4942,13 +4936,13 @@
         <x:v>prompt-03-inbox-followup.md</x:v>
       </x:c>
       <x:c r="C28" s="9" t="n">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D28" s="19" t="str">
-        <x:v>回复：复用草稿与发送，维护 threadId、In-Reply-To、References 和主题关系。在指定收件端验证属于目标会话。只有实际收到消息才标已回复；区分人工、自动和未知，不能把自动回复作为人工回复指标。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="52" customHeight="1">
+        <x:v>Confirmed Constraints: Personal workspaces can connect to multiple Gmail mailboxes, teams are reserved; default English interface with support for Simplified Chinese, email language is independent; Finance is core, Academic is placeholder and contract; no automated email sequences in any phase. All modules are independent and usable, no forced step-by-step wizard. Do not treat Mock or HTML demos as real integrations.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="86" customHeight="1">
       <x:c r="A29" s="5" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -4956,13 +4950,13 @@
         <x:v>prompt-03-inbox-followup.md</x:v>
       </x:c>
       <x:c r="C29" s="5" t="n">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D29" s="18" t="str">
-        <x:v>保护：新回复暂停该联系人的既有未发排期并提示检查，用户明确确认后可继续。这不是新建自动跟进。硬退信地址、退订及明确拒绝进入工作区级 suppression；跨邮箱和活动均执行。提供有效退订入口和手动标记，模糊自然语言只作辅助。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="52" customHeight="1">
+        <x:v>Admin backend is listed as Soon, not part of P1–P4 implementation; only retain Coming Soon entry and scope description, no real management operations. Platform admin and personal workspace owner are different roles.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="154" customHeight="1">
       <x:c r="A30" s="9" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -4970,13 +4964,13 @@
         <x:v>prompt-03-inbox-followup.md</x:v>
       </x:c>
       <x:c r="C30" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D30" s="19" t="str">
-        <x:v>手动跟进：FollowUpTask 关联联系人/会话，支持时间、备注、完成、改期、取消。到期只显示平台提醒；用户主动点击才进入原会话写信，可选模板/AI，再明确发送或排期。收到回复时提示检查关联任务，不自动发送。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="52" customHeight="1">
+        <x:v>First check workspace, AGENTS.md, and implemented code, provide a short implementation order, then proceed with development. Continue with existing data and modules, do not rebuild the entire project. Third-party capabilities check current official documentation; without credentials, explicitly Mock, real failures cannot be silently rolled back. Deliver code, migration, startup instructions, key validations, and real unverified items. Real sending only uses user-specified test recipients.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="69" customHeight="1">
       <x:c r="A31" s="5" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -4984,13 +4978,13 @@
         <x:v>prompt-03-inbox-followup.md</x:v>
       </x:c>
       <x:c r="C31" s="5" t="n">
-        <x:v>9</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D31" s="18" t="str">
-        <x:v>异常：界面显示最后同步时间、失败原因和权限状态；同步失败时暂停需要最新回复检查的排期。说明回复到达与发信之间仍存在的外部竞态，不承诺绝对零误发。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="52" customHeight="1">
+        <x:v>Develop Phase 3 on top of Phases 1 and 2: centralized Inbox, original conversation reply, manual follow-up, and protection for existing scheduling. Do not develop auto next email.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="137" customHeight="1">
       <x:c r="A32" s="9" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -4998,96 +4992,94 @@
         <x:v>prompt-03-inbox-followup.md</x:v>
       </x:c>
       <x:c r="C32" s="9" t="n">
-        <x:v>10</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D32" s="19" t="str">
-        <x:v>验收：指定测试邮箱真实回复出现在 Inbox；重复/乱序同步不重复消息；游标恢复；归档状态正确；新回复暂停排期；跟进到期绝不发信；保留一期与二期回归。无真实凭据如实标记验证缺口。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="44" customHeight="1">
+        <x:v>Sync: First read recent 30 days and paginate, persist history cursor, incremental polling defaults to two minutes and can be manually refreshed. Cursor expiration triggers sync recovery; ongoing old sessions continue tracking. Associate by workspace/mailbox/provider message/thread ID and deduplicate, messages sent and received outside the platform in Gmail can also enter the conversation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="137" customHeight="1">
       <x:c r="A33" s="5" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B33" s="5" t="str">
-        <x:v>prompt-04-campaigns-polish.md</x:v>
+        <x:v>prompt-03-inbox-followup.md</x:v>
       </x:c>
       <x:c r="C33" s="5" t="n">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D33" s="18" t="str">
-        <x:v>请开发 Connact.ai 第 4 期：批量活动模板与统计。</x:v>
+        <x:v>Inbox: Three columns for filtering, conversation list, body and reply editor/contact sidebar. Support filtering by email, domain, unread, pending reply, and intent; unknown domain does not automatically fall under Finance. Read and archive sync with Gmail; notes, intent, and reminders only in the platform. Clean HTML, remote images default not loaded; attachments show metadata and available entry points.</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="120" customHeight="1">
       <x:c r="A34" s="9" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B34" s="9" t="str">
-        <x:v>prompt-04-campaigns-polish.md</x:v>
+        <x:v>prompt-03-inbox-followup.md</x:v>
       </x:c>
       <x:c r="C34" s="9" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D34" s="19" t="str">
-        <x:v>已确认约束：个人工作区可连接多个 Gmail，团队仅预留；默认英文界面并支持简体中文，邮件语言独立；Finance 是核心，Academic 仅占位与契约；四期均不做自动序列。所有模块独立可用，不强制分步向导。不要把 Mock 或 HTML 演示当作真实集成。
-管理员后端已列为 Soon 待排期，不属于 P1–P4 的实现范围；只保留 Coming Soon 入口与范围说明，不开放真实管理操作。平台管理员与个人工作区 Owner 是不同角色。
-先检查工作区、AGENTS.md 和已实现代码，给出简短实施顺序后直接开发。延续已有数据和模块，不重建整个项目。第三方能力查当前官方文档；没有凭据可显式 Mock，真实失败不能偷偷回退模拟。交付代码、迁移、启动说明、关键验证及真实未验证项。涉及真实发信仅用用户指定测试收件人。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="52" customHeight="1">
+        <x:v>Reply: Reuse draft and sending, maintain threadId, In-Reply-To, References, and subject relationship. Validate that the reply belongs to the target conversation at the specified recipient. Only mark as replied if the message is actually received; distinguish manual, auto, and unknown, cannot treat auto replies as manual reply metrics.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="137" customHeight="1">
       <x:c r="A35" s="5" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B35" s="5" t="str">
-        <x:v>prompt-04-campaigns-polish.md</x:v>
+        <x:v>prompt-03-inbox-followup.md</x:v>
       </x:c>
       <x:c r="C35" s="5" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D35" s="18" t="str">
+        <x:v>Protection: New replies pause existing unsent scheduling for the contact and prompt user to check, user confirmation is required to continue. This is not creating a new auto follow-up. Hard bounce addresses, unsubscribe, and explicit rejection enter workspace-level suppression; cross-mailbox and activity-wide execution. Provide valid unsubscribe entry and manual marking, ambiguous natural language only as auxiliary.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="120" customHeight="1">
+      <x:c r="A36" s="9" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D35" s="18" t="str">
-        <x:v>在前三期代码上开发第四期：批量活动、模板/Snippet 管理、基础统计、设置完善与 Academic 契约。当前仍不开发自动邮件序列、团队协作、计费或 Outlook 真实接入。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="52" customHeight="1">
-      <x:c r="A36" s="9" t="n">
-        <x:v>4</x:v>
-      </x:c>
       <x:c r="B36" s="9" t="str">
-        <x:v>prompt-04-campaigns-polish.md</x:v>
+        <x:v>prompt-03-inbox-followup.md</x:v>
       </x:c>
       <x:c r="C36" s="9" t="n">
-        <x:v>4</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D36" s="19" t="str">
-        <x:v>Campaign 定义：一批用户明确批准的独立邮件；没有首封后自动产生第二封的能力。保存 CampaignRecipient 的联系人、画像版本、内容快照、邮箱、时间和结果。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="52" customHeight="1">
+        <x:v>Manual Follow-Up: FollowUpTask associates with contact/session, supports time, note, completion, reschedule, cancel. Only platform reminder is shown on expiration; user must click to enter original session writing, optional template/AI, then confirm send or schedule. Prompt to check associated tasks upon receiving a reply, do not auto send.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="86" customHeight="1">
       <x:c r="A37" s="5" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B37" s="5" t="str">
-        <x:v>prompt-04-campaigns-polish.md</x:v>
+        <x:v>prompt-03-inbox-followup.md</x:v>
       </x:c>
       <x:c r="C37" s="5" t="n">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D37" s="18" t="str">
-        <x:v>用户选择名单后逐人生成并预览邮件，统一显示缺失变量、重复联系人、无邮箱、屏蔽、附件、限额和时间问题。允许明确排除异常人，不能静默跳过。用户批准后逐人分别发送，不使用群体 To/CC。复用二期调度、幂等和三期回复保护。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="52" customHeight="1">
+        <x:v>Exception: Interface shows last sync time, failure reason, and permission status; sync failure pauses scheduling requiring latest reply check. Explain the external race condition between reply arrival and sending, do not guarantee zero mis-sends.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="103" customHeight="1">
       <x:c r="A38" s="9" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B38" s="9" t="str">
-        <x:v>prompt-04-campaigns-polish.md</x:v>
+        <x:v>prompt-03-inbox-followup.md</x:v>
       </x:c>
       <x:c r="C38" s="9" t="n">
-        <x:v>6</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D38" s="19" t="str">
-        <x:v>支持活动暂停/恢复/终止、单人退出、部分失败和进度。恢复重新计算合法窗口，不瞬间补发逾期任务。重试 unknown 先核对，禁止无脑重发。内容批准后模板更新不影响既有任务。</x:v>
+        <x:v>Acceptance: Specified test email real reply appears in Inbox; duplicate/unordered sync does not duplicate messages; cursor recovery; archive status correct; new reply pauses scheduling; follow-up expiration never sends; retain Phase 1 and 2 regression. Truthfully mark validation gaps without real credentials.</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="52" customHeight="1">
@@ -5098,13 +5090,13 @@
         <x:v>prompt-04-campaigns-polish.md</x:v>
       </x:c>
       <x:c r="C39" s="5" t="n">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D39" s="18" t="str">
-        <x:v>Templates/Snippets：Finance 分类、创建/编辑/版本/归档；Academic 仅示例分类。批量 AI 使用与一期一致的事实和人工采纳规则，不在后台临时编造个性化内容。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="52" customHeight="1">
+        <x:v>Please develop Connact.ai Phase 4: Batch Campaign Templates and Analytics.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="137" customHeight="1">
       <x:c r="A40" s="9" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -5112,13 +5104,13 @@
         <x:v>prompt-04-campaigns-polish.md</x:v>
       </x:c>
       <x:c r="C40" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D40" s="19" t="str">
-        <x:v>Analytics：正式发送邮件数和去重人数、人工回复人数、已检测退信、退订、活动进度和手动任务。明确事件、时间窗、分母及去重口径。测试和Mock独立，不造送达/打开/点击率。完善配置、数据导出/删除、错误和中英文文案。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" ht="69" customHeight="1">
+        <x:v>Confirmed Constraints: Personal workspaces can connect to multiple Gmail mailboxes, teams are reserved; default English interface with support for Simplified Chinese, email language is independent; Finance is core, Academic is placeholder and contract; no automated email sequences in any phase. All modules are independent and usable, no forced step-by-step wizard. Do not treat Mock or HTML demos as real integrations.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="86" customHeight="1">
       <x:c r="A41" s="5" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -5126,13 +5118,13 @@
         <x:v>prompt-04-campaigns-polish.md</x:v>
       </x:c>
       <x:c r="C41" s="5" t="n">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D41" s="18" t="str">
-        <x:v>Academic：保持 Coming Soon；设计学术画像及 Mentor 扩展、候选列表与共享模块关联。实现 MentorDataProvider/MentorMatchingProvider 契约测试，预留 JSONL/SQLite/Postgres/External 注册骨架。未实现返回明确 Unavailable，不伪造导师或空成功结果。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="52" customHeight="1">
+        <x:v>Admin backend is listed as Soon, not part of P1–P4 implementation; only retain Coming Soon entry and scope description, no real management operations. Platform admin and personal workspace owner are different roles.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="154" customHeight="1">
       <x:c r="A42" s="9" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -5140,16 +5132,128 @@
         <x:v>prompt-04-campaigns-polish.md</x:v>
       </x:c>
       <x:c r="C42" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D42" s="19" t="str">
+        <x:v>First check workspace, AGENTS.md, and implemented code, provide a short implementation order, then proceed with development. Continue with existing data and modules, do not rebuild the entire project. Third-party capabilities check current official documentation; without credentials, explicitly Mock, real failures cannot be silently rolled back. Deliver code, migration, startup instructions, key validations, and real unverified items. Real sending only uses user-specified test recipients.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="103" customHeight="1">
+      <x:c r="A43" s="5" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B43" s="5" t="str">
+        <x:v>prompt-04-campaigns-polish.md</x:v>
+      </x:c>
+      <x:c r="C43" s="5" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D43" s="18" t="str">
+        <x:v>Develop Phase 4 on top of Phases 1–3: batch campaign, template/snippet management, basic analytics, configuration refinement, and Academic contract. Still no development of automated email sequences, team collaboration, billing, or Outlook real integration.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="86" customHeight="1">
+      <x:c r="A44" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B44" s="9" t="str">
+        <x:v>prompt-04-campaigns-polish.md</x:v>
+      </x:c>
+      <x:c r="C44" s="9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D44" s="19" t="str">
+        <x:v>Campaign Definition: A batch of independently approved emails by users; no capability to automatically generate second emails after the first. Save CampaignRecipient's contact, persona version, content snapshot, email, time, and result.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="137" customHeight="1">
+      <x:c r="A45" s="5" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B45" s="5" t="str">
+        <x:v>prompt-04-campaigns-polish.md</x:v>
+      </x:c>
+      <x:c r="C45" s="5" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D45" s="18" t="str">
+        <x:v>After user selects the list, generate and preview emails for each individual, uniformly display missing variables, duplicate contacts, no email, block, attachments, limits, and time issues. Allow explicit exclusion of abnormal individuals, cannot silently skip. After user approval, send individually, do not use group To/CC. Reuse Phase 2 scheduling, idempotency, and Phase 3 reply protection.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="103" customHeight="1">
+      <x:c r="A46" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B46" s="9" t="str">
+        <x:v>prompt-04-campaigns-polish.md</x:v>
+      </x:c>
+      <x:c r="C46" s="9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D46" s="19" t="str">
+        <x:v>Support campaign pause/resume/termination, individual exit, partial failure, and progress. Resume recalculates valid window, does not instantly resend overdue tasks. Retry unknowns first verify, prohibit blind resends. Content approval does not affect existing tasks with template updates.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="86" customHeight="1">
+      <x:c r="A47" s="5" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B47" s="5" t="str">
+        <x:v>prompt-04-campaigns-polish.md</x:v>
+      </x:c>
+      <x:c r="C47" s="5" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D47" s="18" t="str">
+        <x:v>Templates/Snippets: Finance classification, create/edit/version/archive; Academic only example classification. Batch AI uses the same facts and manual adoption rules as Phase 1, no temporary fabrication of personalized content in the background.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="120" customHeight="1">
+      <x:c r="A48" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B48" s="9" t="str">
+        <x:v>prompt-04-campaigns-polish.md</x:v>
+      </x:c>
+      <x:c r="C48" s="9" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D42" s="19" t="str">
-        <x:v>验收：逐人预览与发出内容一致；重复启动不重复发；暂停/退出/回复/退订生效；统计可从事件核对。完成四期回归、运行文档、真实验证记录和公开上线外部事项清单。不要把完成设计文档或演示当作产品已完成。</x:v>
+      <x:c r="D48" s="19" t="str">
+        <x:v>Analytics: Formal sent email count and deduplicated users, manually replied users, detected bounces, unsubscribes, campaign progress, and manual tasks. Clearly define events, time window, denominator, and deduplication criteria. Test and Mock are independent, no fabricated delivery/open/click rates. Improve configuration, data export/delete, errors, and Chinese/English copy.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="120" customHeight="1">
+      <x:c r="A49" s="5" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B49" s="5" t="str">
+        <x:v>prompt-04-campaigns-polish.md</x:v>
+      </x:c>
+      <x:c r="C49" s="5" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D49" s="18" t="str">
+        <x:v>Academic: Keep Coming Soon; design academic persona and Mentor extension, candidate list, and shared module association. Implement MentorDataProvider/MentorMatchingProvider contract testing, reserve JSONL/SQLite/PostgreSQL/External registration skeleton. Return explicit Unavailable if not implemented, do not fabricate mentors or empty success results.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="137" customHeight="1">
+      <x:c r="A50" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B50" s="9" t="str">
+        <x:v>prompt-04-campaigns-polish.md</x:v>
+      </x:c>
+      <x:c r="C50" s="9" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D50" s="19" t="str">
+        <x:v>Acceptance: Preview and sent content for each individual are consistent; duplicate launch does not duplicate send; pause/exit/reply/unsubscribe take effect; statistics can be verified from events. Complete Phase 4 regression, operation documentation, real validation records, and public launch external matters list. Do not treat completed design documents or demos as product completion.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdd415a02c0f4a82"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3d85346c1594abc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5166,7 +5270,7 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="2" t="str">
-        <x:v>来源与使用边界</x:v>
+        <x:v>Sources and Usage Boundaries</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
@@ -5174,7 +5278,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="3" t="str">
-        <x:v>官方资料核对日期 2026-09-06；产品范围来自当前对话，设计默认值可调整。</x:v>
+        <x:v>Official Source Verification Date 2026-09-06; product scope comes from the current conversation, design default values can be adjusted</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -5191,13 +5295,13 @@
         <x:v>ID</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
-        <x:v>来源</x:v>
+        <x:v>Source</x:v>
       </x:c>
       <x:c r="C4" s="8" t="str">
-        <x:v>地址或位置</x:v>
+        <x:v>Address or Location</x:v>
       </x:c>
       <x:c r="D4" s="8" t="str">
-        <x:v>用途</x:v>
+        <x:v>Purpose</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
@@ -5205,13 +5309,13 @@
         <x:v>S01</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>用户确认范围</x:v>
+        <x:v>User confirmed scope</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>本对话 2026-09-06</x:v>
+        <x:v>This conversation 2026-09-06</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>个人多Gmail、英文默认、手动跟进、四期无自动序列</x:v>
+        <x:v>Personal multi-Gmail, English default, manual follow-up, four phases with no automated email sequence</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="64" customHeight="1">
@@ -5219,14 +5323,14 @@
         <x:v>S02</x:v>
       </x:c>
       <x:c r="B6" s="9" t="str">
-        <x:v>Apollo 与 LinkedIn 公开搜索</x:v>
+        <x:v>Apollo and LinkedIn public search</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
         <x:v>https://docs.apollo.io/reference/people-api-search
 https://serpapi.com/search-api</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>Apollo 人员搜索与邮箱补充分离；SerpAPI 经 Google 检索 LinkedIn 公开页，覆盖取决于索引。双源协同待实现验证</x:v>
+        <x:v>Apollo people search and email enrichment are separated; SerpAPI is indexed via Google for LinkedIn public pages, coverage depends on indexing. Dual-source collaboration is pending verification</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="64" customHeight="1">
@@ -5234,13 +5338,13 @@
         <x:v>S03</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>Gmail OAuth 权限</x:v>
+        <x:v>Gmail OAuth permissions</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
         <x:v>https://developers.google.com/workspace/gmail/api/auth/scopes</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
-        <x:v>按实际功能申请；公开验证独立于本地开发</x:v>
+        <x:v>Apply based on actual functionality; public verification is independent of local development</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="64" customHeight="1">
@@ -5248,13 +5352,13 @@
         <x:v>S04</x:v>
       </x:c>
       <x:c r="B8" s="9" t="str">
-        <x:v>Gmail 同步</x:v>
+        <x:v>Gmail synchronization</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
         <x:v>https://developers.google.com/workspace/gmail/api/guides/sync</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
-        <x:v>初次和增量同步；游标失效需要恢复</x:v>
+        <x:v>Initial and incremental synchronization; cursor failure requires recovery</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="64" customHeight="1">
@@ -5262,13 +5366,13 @@
         <x:v>S05</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>Gmail 会话</x:v>
+        <x:v>Gmail session</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
         <x:v>https://developers.google.com/workspace/gmail/api/guides/threads</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>回复保留threadId和消息头关系</x:v>
+        <x:v>Reply retains threadId and message header relationship</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="64" customHeight="1">
@@ -5276,13 +5380,13 @@
         <x:v>S06</x:v>
       </x:c>
       <x:c r="B10" s="9" t="str">
-        <x:v>Tiptap Mention 扩展</x:v>
+        <x:v>Tiptap Mention extension</x:v>
       </x:c>
       <x:c r="C10" s="9" t="str">
         <x:v>https://tiptap.dev/docs/editor/extensions/nodes/mention</x:v>
       </x:c>
       <x:c r="D10" s="9" t="str">
-        <x:v>参考节点交互机制；变量节点需自定义设计</x:v>
+        <x:v>Reference node interaction mechanism; variable nodes require custom design</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="64" customHeight="1">
@@ -5290,13 +5394,13 @@
         <x:v>D01</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>状态说明</x:v>
+        <x:v>Status Notes</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
-        <x:v>功能清单 I 列</x:v>
+        <x:v>Feature List Column I</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
-        <x:v>仅表示产品开发实施；当前均未开始</x:v>
+        <x:v>Only indicates product development implementation; all are currently unstarted</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="64" customHeight="1">
@@ -5304,13 +5408,13 @@
         <x:v>D02</x:v>
       </x:c>
       <x:c r="B12" s="9" t="str">
-        <x:v>验证说明</x:v>
+        <x:v>Verification Notes</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>功能清单 J/K 列</x:v>
+        <x:v>Feature List Columns J/K</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
-        <x:v>Mock与真实验证分开，真实需提供脱敏证据</x:v>
+        <x:v>Mock and real verification are separated; real verification requires desensitized evidence</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="64" customHeight="1">
@@ -5318,13 +5422,13 @@
         <x:v>D03</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>设计默认值</x:v>
+        <x:v>Design Default Values</x:v>
       </x:c>
       <x:c r="C13" s="5" t="str">
-        <x:v>Word第14节</x:v>
+        <x:v>Word Section 14</x:v>
       </x:c>
       <x:c r="D13" s="5" t="str">
-        <x:v>10MB上传、一秒防抖、两分钟轮询不是服务商承诺</x:v>
+        <x:v>10MB upload, one-second debounce, two-minute polling are not service provider commitments</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="64" customHeight="1">
@@ -5332,13 +5436,13 @@
         <x:v>D04</x:v>
       </x:c>
       <x:c r="B14" s="9" t="str">
-        <x:v>HTML演示</x:v>
+        <x:v>HTML Demo</x:v>
       </x:c>
       <x:c r="C14" s="9" t="str">
         <x:v>connact-ai-workflow-demo.html</x:v>
       </x:c>
       <x:c r="D14" s="9" t="str">
-        <x:v>全部示例为虚构；无网络、无真实上传解析或发送</x:v>
+        <x:v>All examples are fictional; no network, no real upload parsing or sending</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="64" customHeight="1">
@@ -5346,19 +5450,19 @@
         <x:v>D05</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>统计口径</x:v>
+        <x:v>Statistical Scope</x:v>
       </x:c>
       <x:c r="C15" s="5" t="str">
-        <x:v>Word第13节</x:v>
+        <x:v>Word Section 13</x:v>
       </x:c>
       <x:c r="D15" s="5" t="str">
-        <x:v>回复率使用同一触达cohort并标观察截止时间</x:v>
+        <x:v>Response rate uses the same touchpoint cohort and marks the observation cutoff time</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc0ff0e54d6de4504"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b9dd131c3364853"/>
   </x:tableParts>
 </x:worksheet>
 </file>